--- a/example/DEMO_HK_Answer_Key.xlsx
+++ b/example/DEMO_HK_Answer_Key.xlsx
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,10 +142,11 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -235,9 +236,34 @@
     <author>BAV Trainer</author>
   </authors>
   <commentList>
+    <comment ref="F23" authorId="0" shapeId="0">
+      <text>
+        <t>Relate tax expense to pretax income using the model's sign convention.</t>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0">
+      <text>
+        <t>Combine interest expense and interest income into the financing result.</t>
+      </text>
+    </comment>
+    <comment ref="F25" authorId="0" shapeId="0">
+      <text>
+        <t>Apply the effective tax rate once to net interest.</t>
+      </text>
+    </comment>
     <comment ref="F26" authorId="0" shapeId="0">
       <text>
         <t>Reformulate net income to operating profit after tax.</t>
+      </text>
+    </comment>
+    <comment ref="F29" authorId="0" shapeId="0">
+      <text>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+      </text>
+    </comment>
+    <comment ref="F30" authorId="0" shapeId="0">
+      <text>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="F31" authorId="0" shapeId="0">
@@ -245,14 +271,44 @@
         <t>Sum operating WC assets minus operating WC liabilities.</t>
       </text>
     </comment>
+    <comment ref="F32" authorId="0" shapeId="0">
+      <text>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+      </text>
+    </comment>
+    <comment ref="F33" authorId="0" shapeId="0">
+      <text>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+      </text>
+    </comment>
+    <comment ref="F34" authorId="0" shapeId="0">
+      <text>
+        <t>Operating long-term assets less operating long-term liabilities.</t>
+      </text>
+    </comment>
     <comment ref="F35" authorId="0" shapeId="0">
       <text>
         <t>NOWC plus net operating long-term assets.</t>
       </text>
     </comment>
+    <comment ref="F36" authorId="0" shapeId="0">
+      <text>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+      </text>
+    </comment>
+    <comment ref="F37" authorId="0" shapeId="0">
+      <text>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+      </text>
+    </comment>
     <comment ref="F38" authorId="0" shapeId="0">
       <text>
         <t>Financial liabilities minus financial assets.</t>
+      </text>
+    </comment>
+    <comment ref="F39" authorId="0" shapeId="0">
+      <text>
+        <t>Use the operating/financing identity linking NOA, Net Debt, and Equity.</t>
       </text>
     </comment>
   </commentList>
@@ -270,14 +326,29 @@
         <t>NOPAT divided by average NOA.</t>
       </text>
     </comment>
+    <comment ref="E6" authorId="0" shapeId="0">
+      <text>
+        <t>Relate net interest after tax to average net debt.</t>
+      </text>
+    </comment>
     <comment ref="E7" authorId="0" shapeId="0">
       <text>
         <t>Operating return minus after-tax cost of debt.</t>
       </text>
     </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>Relate average net debt to average reformulated equity.</t>
+      </text>
+    </comment>
     <comment ref="E9" authorId="0" shapeId="0">
       <text>
         <t>ROE = RNOA + FLEV × Spread.</t>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0">
+      <text>
+        <t>Relate net income to average reformulated equity.</t>
       </text>
     </comment>
   </commentList>
@@ -623,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -680,7 +751,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>NOPAT (latest fiscal year)</t>
+          <t>Effective tax rate (latest fiscal year)</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -690,7 +761,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>F26</t>
+          <t>F23</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -705,7 +776,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Net Operating Working Capital (NOWC)</t>
+          <t>Net interest (latest fiscal year)</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -715,12 +786,12 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>F31</t>
+          <t>F24</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>nopat_fy</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -730,7 +801,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Net Operating Assets (NOA)</t>
+          <t>Net interest after tax</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -740,12 +811,12 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>F35</t>
+          <t>F25</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>nowc_agg</t>
+          <t>effective_tax_rate_fy, net_interest_fy</t>
         </is>
       </c>
     </row>
@@ -755,7 +826,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Net Debt</t>
+          <t>NOPAT (latest fiscal year)</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -765,12 +836,12 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>F38</t>
+          <t>F26</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>noa_agg</t>
+          <t>net_interest_after_tax_fy</t>
         </is>
       </c>
     </row>
@@ -780,22 +851,22 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Return on Net Operating Assets (RNOA)</t>
+          <t>Operating working capital assets</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>ALT DuPont</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>F29</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>nopat_fy, noa_agg</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -805,22 +876,22 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Operating Spread (RNOA − After-tax CoD)</t>
+          <t>Operating working capital liabilities</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>ALT DuPont</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>F30</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>rnoa</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -830,22 +901,22 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>ROE decomposition</t>
+          <t>Net Operating Working Capital (NOWC)</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>ALT DuPont</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>E9</t>
+          <t>F31</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>rnoa, spread</t>
+          <t>owca_agg, owcl_agg</t>
         </is>
       </c>
     </row>
@@ -855,22 +926,22 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Base case Y1 revenue forecast</t>
+          <t>Operating long-term assets</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Model_Base</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>G21</t>
+          <t>F32</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>nopat_fy</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -880,22 +951,22 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Base case Y1 NOPAT</t>
+          <t>Operating long-term liabilities</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Model_Base</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>G27</t>
+          <t>F33</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>model_sales_y1</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -905,22 +976,22 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Year 1 abnormal earnings</t>
+          <t>Net operating long-term assets (NOLA)</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Model_Base</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>G29</t>
+          <t>F34</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>model_nopat_y1</t>
+          <t>olta_agg, oltl_agg</t>
         </is>
       </c>
     </row>
@@ -930,22 +1001,22 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Terminal value (PV of abnormal earnings)</t>
+          <t>Net Operating Assets (NOA)</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Model_Base</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>G37</t>
+          <t>F35</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>model_ae_y1</t>
+          <t>nowc_agg, nola_agg</t>
         </is>
       </c>
     </row>
@@ -955,22 +1026,22 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Intrinsic value per share</t>
+          <t>Financial assets</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Model_Base</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>G40</t>
+          <t>F36</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>model_tv</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -980,20 +1051,370 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
+          <t>Financial liabilities</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Condensed Financials</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>F37</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Condensed Financials</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>F38</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>financial_assets_agg, financial_liabilities_agg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Reformulated equity</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Condensed Financials</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>F39</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>noa_agg, net_debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Return on Net Operating Assets (RNOA)</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>nopat_fy, noa_agg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>After-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>net_interest_after_tax_fy, net_debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Operating Spread (RNOA − After-tax CoD)</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>rnoa, after_tax_cod</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Financial leverage (FLEV)</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>net_debt, equity_reformulated_fy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>ROE decomposition</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>E9</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>rnoa, spread, flev</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Actual ROE</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>equity_reformulated_fy</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Base case Y1 revenue forecast</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Model_Base</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>G21</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>nopat_fy</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Base case Y1 NOPAT</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Model_Base</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>G27</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>model_sales_y1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Year 1 abnormal earnings</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Model_Base</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>G29</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>model_nopat_y1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Terminal value (PV of abnormal earnings)</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Model_Base</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>G37</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>model_ae_y1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Intrinsic value per share</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Model_Base</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>G40</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>model_tv</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
           <t>Probability-weighted IVPS</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Scenario_Summary</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>E8</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>model_ivps</t>
         </is>
@@ -1037,8 +1458,8 @@
           <t>IVPS</t>
         </is>
       </c>
-      <c r="D3" s="31" t="n"/>
-      <c r="E3" s="31" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="32" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
@@ -1046,7 +1467,7 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="B4" s="32" t="n">
+      <c r="B4" s="33" t="n">
         <v>0.25</v>
       </c>
       <c r="C4" s="14">
@@ -1060,7 +1481,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="33" t="n">
         <v>0.5</v>
       </c>
       <c r="C5" s="14">
@@ -1074,7 +1495,7 @@
           <t>Bull</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
+      <c r="B6" s="33" t="n">
         <v>0.25</v>
       </c>
       <c r="C6" s="14">
@@ -1089,7 +1510,7 @@
           <t>Weighted IVPS</t>
         </is>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>SUMPRODUCT(B4:B6,C4:C6)</f>
         <v/>
       </c>
@@ -1106,7 +1527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1189,7 +1610,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nopat_fy</t>
+          <t>effective_tax_rate_fy</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1197,17 +1618,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NOPAT (latest fiscal year)</t>
+          <t>Effective tax rate (latest fiscal year)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Reformulate net income to operating profit after tax.</t>
+          <t>Relate tax expense to pretax income using the model's sign convention.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>condensed.nopat.latest_fy</t>
+          <t>condensed.effective_tax_rate.latest_fy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1222,22 +1643,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>F26</t>
+          <t>F23</t>
         </is>
       </c>
       <c r="I2">
-        <f>F18+F25</f>
+        <f>IF(F19=0,0,-F20/F19)</f>
         <v/>
       </c>
       <c r="J2" t="n">
-        <v>4150.866462793068</v>
+        <v>0.1698267074413863</v>
       </c>
       <c r="K2" t="n">
         <v>0.01</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Start from Net Income on the Income Statement.|Add back after-tax net interest: Net Interest × (1 − Tax Rate).|NOPAT = Net Income + Net Interest After Tax.</t>
+          <t>Effective tax rate uses pretax income in the denominator.|Preserve the model's sign convention for tax expense.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1249,7 +1670,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nowc_agg</t>
+          <t>net_interest_fy</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1257,17 +1678,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Net Operating Working Capital (NOWC)</t>
+          <t>Net interest (latest fiscal year)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sum operating WC assets minus operating WC liabilities.</t>
+          <t>Combine interest expense and interest income into the financing result.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>condensed.nowc.latest_fy</t>
+          <t>condensed.net_interest.latest_fy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1282,27 +1703,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>F31</t>
+          <t>F24</t>
         </is>
       </c>
       <c r="I3">
-        <f>F29-F30</f>
+        <f>-(F21+F22)</f>
         <v/>
       </c>
       <c r="J3" t="n">
-        <v>1375</v>
+        <v>95</v>
       </c>
       <c r="K3" t="n">
         <v>0.01</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>nopat_fy</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Use SUMIF over the classification column for 'Operating Working Capital Asset'.|Subtract SUMIF for 'Operating Working Capital Liability'.|NOWC = Op. WC Assets − Op. WC Liabilities.</t>
+          <t>Net interest consolidates interest expense and interest income.|Missing optional interest lines are treated as zero.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1314,7 +1730,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>noa_agg</t>
+          <t>net_interest_after_tax_fy</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1322,17 +1738,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Net Operating Assets (NOA)</t>
+          <t>Net interest after tax</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NOWC plus net operating long-term assets.</t>
+          <t>Apply the effective tax rate once to net interest.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>condensed.noa.latest_fy</t>
+          <t>condensed.net_interest_after_tax.latest_fy</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1347,27 +1763,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>F35</t>
+          <t>F25</t>
         </is>
       </c>
       <c r="I4">
-        <f>F31+F34</f>
+        <f>F24*(1-F23)</f>
         <v/>
       </c>
       <c r="J4" t="n">
-        <v>7950</v>
+        <v>78.86646279306829</v>
       </c>
       <c r="K4" t="n">
         <v>0.01</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>nowc_agg</t>
+          <t>effective_tax_rate_fy,net_interest_fy</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Net Operating LT Assets = Op. LT Assets − Op. LT Liabilities (SUMIF).|NOA = NOWC + Net Operating LT Assets.</t>
+          <t>After-tax net interest = Net Interest × (1 − Effective Tax Rate).|Do not tax-adjust a rate that is already after tax.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1379,7 +1795,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>net_debt</t>
+          <t>nopat_fy</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1387,17 +1803,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Net Debt</t>
+          <t>NOPAT (latest fiscal year)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Financial liabilities minus financial assets.</t>
+          <t>Reformulate net income to operating profit after tax.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>condensed.net_debt.latest_fy</t>
+          <t>condensed.nopat.latest_fy</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1412,27 +1828,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>F38</t>
+          <t>F26</t>
         </is>
       </c>
       <c r="I5">
-        <f>F37-F36</f>
+        <f>F18+F25</f>
         <v/>
       </c>
       <c r="J5" t="n">
-        <v>-750</v>
+        <v>4150.866462793068</v>
       </c>
       <c r="K5" t="n">
         <v>0.01</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>noa_agg</t>
+          <t>net_interest_after_tax_fy</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Net Debt = SUMIF(Financial Liability) − SUMIF(Financial Asset).|Positive net debt means the firm carries net financial obligations.</t>
+          <t>Start from Net Income on the Income Statement.|Add back after-tax net interest: Net Interest × (1 − Tax Rate).|NOPAT = Net Income + Net Interest After Tax.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1444,7 +1860,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rnoa</t>
+          <t>owca_agg</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1452,52 +1868,47 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Return on Net Operating Assets (RNOA)</t>
+          <t>Operating working capital assets</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NOPAT divided by average NOA.</t>
+          <t>Aggregate the classified balance-sheet detail with the classification column.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>dupont.rnoa.latest_comparable</t>
+          <t>condensed.owca.latest_fy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>dupont</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ALT DuPont</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>F29</t>
         </is>
       </c>
       <c r="I6">
-        <f>'Condensed Financials'!F26/(('Condensed Financials'!F35+'Condensed Financials'!E35)/2)</f>
+        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",G$6:G$15)</f>
         <v/>
       </c>
       <c r="J6" t="n">
-        <v>0.5545579776610646</v>
+        <v>2250</v>
       </c>
       <c r="K6" t="n">
         <v>0.01</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>nopat_fy,noa_agg</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>RNOA = NOPAT / Average NOA.|Average NOA = (Beginning NOA + Ending NOA) / 2.</t>
+          <t>Use SUMIF over the classification column for Operating Working Capital Asset.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1509,7 +1920,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>owcl_agg</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1517,52 +1928,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Operating Spread (RNOA − After-tax CoD)</t>
+          <t>Operating working capital liabilities</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Operating return minus after-tax cost of debt.</t>
+          <t>Aggregate the classified balance-sheet detail with the classification column.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>dupont.spread.latest_comparable</t>
+          <t>condensed.owcl.latest_fy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>dupont</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ALT DuPont</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>F30</t>
         </is>
       </c>
       <c r="I7">
-        <f>E5-E6</f>
+        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",G$6:G$15)</f>
         <v/>
       </c>
       <c r="J7" t="n">
-        <v>0.6827961285441025</v>
+        <v>875</v>
       </c>
       <c r="K7" t="n">
         <v>0.01</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>rnoa</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>After-tax CoD = Net Interest After Tax / Average Net Debt.|Spread = RNOA − After-tax CoD.</t>
+          <t>Use SUMIF over the classification column for Operating Working Capital Liability.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1574,7 +1980,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>roe_decomp</t>
+          <t>nowc_agg</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1582,52 +1988,52 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ROE decomposition</t>
+          <t>Net Operating Working Capital (NOWC)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ROE = RNOA + FLEV × Spread.</t>
+          <t>Sum operating WC assets minus operating WC liabilities.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>dupont.roe_decomposed.latest_comparable</t>
+          <t>condensed.nowc.latest_fy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>dupont</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ALT DuPont</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>E9</t>
+          <t>F31</t>
         </is>
       </c>
       <c r="I8">
-        <f>E5+E8*(E7)</f>
+        <f>F29-F30</f>
         <v/>
       </c>
       <c r="J8" t="n">
-        <v>0.5027160493827161</v>
+        <v>1375</v>
       </c>
       <c r="K8" t="n">
         <v>0.01</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>rnoa,spread</t>
+          <t>owca_agg,owcl_agg</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Financial leverage (FLEV) = Average Net Debt / Average Equity.|ROE (decomposed) = RNOA + FLEV × (RNOA − After-tax CoD).</t>
+          <t>Use SUMIF over the classification column for 'Operating Working Capital Asset'.|Subtract SUMIF for 'Operating Working Capital Liability'.|NOWC = Op. WC Assets − Op. WC Liabilities.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1639,7 +2045,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>model_sales_y1</t>
+          <t>olta_agg</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1647,52 +2053,47 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Base case Y1 revenue forecast</t>
+          <t>Operating long-term assets</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Anchor revenue × (1 + Y1 growth).</t>
+          <t>Aggregate the classified balance-sheet detail with the classification column.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>model.sales.y1</t>
+          <t>condensed.olta.latest_fy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>forecasting</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Model_Base</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>G21</t>
+          <t>F32</t>
         </is>
       </c>
       <c r="I9">
-        <f>'Income Statement'!F7*(1+0.1)</f>
+        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",G$6:G$15)</f>
         <v/>
       </c>
       <c r="J9" t="n">
-        <v>13750</v>
+        <v>8400</v>
       </c>
       <c r="K9" t="n">
         <v>0.01</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>nopat_fy</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Y1 beginning sales = prior fiscal year revenue from Income Statement.|Y1 Sales = Anchor Revenue × (1 + growthVector[0]).</t>
+          <t>Use SUMIF over the classification column for Operating Long-Term Asset.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1704,7 +2105,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>model_nopat_y1</t>
+          <t>oltl_agg</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1712,52 +2113,47 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Base case Y1 NOPAT</t>
+          <t>Operating long-term liabilities</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Forecast sales × NOPAT margin.</t>
+          <t>Aggregate the classified balance-sheet detail with the classification column.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>model.nopat.y1</t>
+          <t>condensed.oltl.latest_fy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>forecasting</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Model_Base</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>G27</t>
+          <t>F33</t>
         </is>
       </c>
       <c r="I10">
-        <f>G21*G22</f>
+        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",G$6:G$15)</f>
         <v/>
       </c>
       <c r="J10" t="n">
-        <v>2062.5</v>
+        <v>1825</v>
       </c>
       <c r="K10" t="n">
         <v>0.01</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>model_sales_y1</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>NOPAT = Sales × marginVector[t].|Margin vector is a blue forecast input.</t>
+          <t>Use SUMIF over the classification column for Operating Long-Term Liability.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1769,7 +2165,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>model_ae_y1</t>
+          <t>nola_agg</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1777,52 +2173,52 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Year 1 abnormal earnings</t>
+          <t>Net operating long-term assets (NOLA)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Residual income: NI − Ke × Equity.</t>
+          <t>Operating long-term assets less operating long-term liabilities.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>model.abnormal_earnings.y1</t>
+          <t>condensed.nola.latest_fy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Model_Base</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>G29</t>
+          <t>F34</t>
         </is>
       </c>
       <c r="I11">
-        <f>G28-$B$5*G26</f>
+        <f>F32-F33</f>
         <v/>
       </c>
       <c r="J11" t="n">
-        <v>1043.756153868829</v>
+        <v>6575</v>
       </c>
       <c r="K11" t="n">
         <v>0.01</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>model_nopat_y1</t>
+          <t>olta_agg,oltl_agg</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Net Income = NOPAT − Net Debt × after-tax cost of debt.|Abnormal Earnings = Net Income − Cost of Equity × Book Equity.</t>
+          <t>NOLA = Operating LT Assets − Operating LT Liabilities.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1834,7 +2230,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>model_tv</t>
+          <t>noa_agg</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1842,52 +2238,52 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Terminal value (PV of abnormal earnings)</t>
+          <t>Net Operating Assets (NOA)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Gordon growth on terminal-year abnormal earnings, discounted.</t>
+          <t>NOWC plus net operating long-term assets.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>model.terminal_value.pv</t>
+          <t>condensed.noa.latest_fy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Model_Base</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>G37</t>
+          <t>F35</t>
         </is>
       </c>
       <c r="I12">
-        <f>P36*P30</f>
+        <f>F31+F34</f>
         <v/>
       </c>
       <c r="J12" t="n">
-        <v>15516.94169433467</v>
+        <v>7950</v>
       </c>
       <c r="K12" t="n">
         <v>0.01</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>model_ae_y1</t>
+          <t>nowc_agg,nola_agg</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>TV = AE₁₀ × (1 + g) / (Ke − g).|Discount TV back 10 years at Ke.</t>
+          <t>Net Operating LT Assets = Op. LT Assets − Op. LT Liabilities (SUMIF).|NOA = NOWC + Net Operating LT Assets.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1899,7 +2295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>model_ivps</t>
+          <t>financial_assets_agg</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1907,52 +2303,47 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Intrinsic value per share</t>
+          <t>Financial assets</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Book equity + PV(abnormal earnings) + PV(terminal value).</t>
+          <t>Aggregate the classified balance-sheet detail with the classification column.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>model.ivps</t>
+          <t>condensed.financial_assets.latest_fy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Model_Base</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>G40</t>
+          <t>F36</t>
         </is>
       </c>
       <c r="I13">
-        <f>G38/G39</f>
+        <f>SUMIF($B$6:$B$15,"Financial Asset",G$6:G$15)</f>
         <v/>
       </c>
       <c r="J13" t="n">
-        <v>34.2372</v>
+        <v>1850</v>
       </c>
       <c r="K13" t="n">
         <v>0.01</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>model_tv</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>IV = Beginning Book Equity + Σ PV(AE) + PV(TV).|IVPS = IV / Diluted Shares Outstanding.</t>
+          <t>Use SUMIF over the classification column for Financial Asset.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1964,7 +2355,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>scenario_weighted</t>
+          <t>financial_liabilities_agg</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1972,55 +2363,960 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Probability-weighted IVPS</t>
+          <t>Financial liabilities</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SUMPRODUCT of scenario IVPS and probabilities.</t>
+          <t>Aggregate the classified balance-sheet detail with the classification column.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>scenario.weighted_ivps</t>
+          <t>condensed.financial_liabilities.latest_fy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scenario_Summary</t>
+          <t>Condensed Financials</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>F37</t>
         </is>
       </c>
       <c r="I14">
-        <f>SUMPRODUCT(B4:B6,C4:C6)</f>
+        <f>SUMIF($B$6:$B$15,"Financial Liability",G$6:G$15)</f>
         <v/>
       </c>
       <c r="J14" t="n">
-        <v>34.0383</v>
+        <v>1100</v>
       </c>
       <c r="K14" t="n">
         <v>0.01</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Use SUMIF over the classification column for Financial Liability.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>net_debt</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Financial liabilities minus financial assets.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>condensed.net_debt.latest_fy</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>accounting</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Condensed Financials</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>F38</t>
+        </is>
+      </c>
+      <c r="I15">
+        <f>F37-F36</f>
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>-750</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>financial_assets_agg,financial_liabilities_agg</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Net Debt = SUMIF(Financial Liability) − SUMIF(Financial Asset).|Positive net debt means the firm carries net financial obligations.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>equity_reformulated_fy</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Reformulated equity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Use the operating/financing identity linking NOA, Net Debt, and Equity.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>condensed.equity.latest_fy</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>accounting</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Condensed Financials</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>F39</t>
+        </is>
+      </c>
+      <c r="I16">
+        <f>F35-F38</f>
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>8700</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>noa_agg,net_debt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Reformulated Equity = NOA − Net Debt.|This identity must reconcile to reported equity within tolerance.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>rnoa</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Return on Net Operating Assets (RNOA)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NOPAT divided by average NOA.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>dupont.rnoa.latest_comparable</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>dupont</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="I17">
+        <f>'Condensed Financials'!F26/(('Condensed Financials'!F35+'Condensed Financials'!E35)/2)</f>
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5545579776610646</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>nopat_fy,noa_agg</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>RNOA = NOPAT / Average NOA.|Average NOA = (Beginning NOA + Ending NOA) / 2.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>after_tax_cod</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>After-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Relate net interest after tax to average net debt.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>dupont.after_tax_cod.latest_comparable</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>dupont</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="I18">
+        <f>'Condensed Financials'!F25/(('Condensed Financials'!F38+'Condensed Financials'!E38)/2)</f>
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.1282381508830379</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>net_interest_after_tax_fy,net_debt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>After-tax CoD = Net Interest After Tax / Average Net Debt.|Do not apply the tax rate a second time.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Operating Spread (RNOA − After-tax CoD)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Operating return minus after-tax cost of debt.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>dupont.spread.latest_comparable</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>dupont</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="I19">
+        <f>E5-E6</f>
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6827961285441025</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>rnoa,after_tax_cod</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>After-tax CoD = Net Interest After Tax / Average Net Debt.|Spread = RNOA − After-tax CoD.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>flev</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial leverage (FLEV)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Relate average net debt to average reformulated equity.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>dupont.flev.latest_comparable</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>dupont</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="I20">
+        <f>(('Condensed Financials'!F38+'Condensed Financials'!E38)/2)/(('Condensed Financials'!F39+'Condensed Financials'!E39)/2)</f>
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.07592592592592592</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>net_debt,equity_reformulated_fy</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>FLEV = Average Net Debt / Average Equity.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>roe_decomp</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ROE decomposition</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ROE = RNOA + FLEV × Spread.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>dupont.roe_decomposed.latest_comparable</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>dupont</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>E9</t>
+        </is>
+      </c>
+      <c r="I21">
+        <f>E5+E8*(E7)</f>
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5027160493827161</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>rnoa,spread,flev</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Financial leverage (FLEV) = Average Net Debt / Average Equity.|ROE (decomposed) = RNOA + FLEV × (RNOA − After-tax CoD).</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>actual_roe</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Actual ROE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Relate net income to average reformulated equity.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>dupont.actual_roe.latest_comparable</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>dupont</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="I22">
+        <f>'Condensed Financials'!F18/(('Condensed Financials'!F39+'Condensed Financials'!E39)/2)</f>
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5027160493827161</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>equity_reformulated_fy</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Actual ROE = Net Income / Average Equity.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>model_sales_y1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Base case Y1 revenue forecast</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Anchor revenue × (1 + Y1 growth).</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>model.sales.y1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>forecasting</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Model_Base</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>G21</t>
+        </is>
+      </c>
+      <c r="I23">
+        <f>'Income Statement'!F7*(1+0.1)</f>
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v>13750</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>nopat_fy</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Y1 beginning sales = prior fiscal year revenue from Income Statement.|Y1 Sales = Anchor Revenue × (1 + growthVector[0]).</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>model_nopat_y1</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Base case Y1 NOPAT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Forecast sales × NOPAT margin.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>model.nopat.y1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>forecasting</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Model_Base</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>G27</t>
+        </is>
+      </c>
+      <c r="I24">
+        <f>G21*G22</f>
+        <v/>
+      </c>
+      <c r="J24" t="n">
+        <v>2062.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>model_sales_y1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>NOPAT = Sales × marginVector[t].|Margin vector is a blue forecast input.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>model_ae_y1</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Year 1 abnormal earnings</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Residual income: NI − Ke × Equity.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>model.abnormal_earnings.y1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Model_Base</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>G29</t>
+        </is>
+      </c>
+      <c r="I25">
+        <f>G28-$B$5*G26</f>
+        <v/>
+      </c>
+      <c r="J25" t="n">
+        <v>1043.756153868829</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>model_nopat_y1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Net Income = NOPAT − Net Debt × after-tax cost of debt.|Abnormal Earnings = Net Income − Cost of Equity × Book Equity.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>model_tv</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Terminal value (PV of abnormal earnings)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Gordon growth on terminal-year abnormal earnings, discounted.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>model.terminal_value.pv</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Model_Base</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>G37</t>
+        </is>
+      </c>
+      <c r="I26">
+        <f>P36*P30</f>
+        <v/>
+      </c>
+      <c r="J26" t="n">
+        <v>15516.94169433467</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>model_ae_y1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>TV = AE₁₀ × (1 + g) / (Ke − g).|Discount TV back 10 years at Ke.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>model_ivps</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Intrinsic value per share</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Book equity + PV(abnormal earnings) + PV(terminal value).</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>model.ivps</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Model_Base</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>G40</t>
+        </is>
+      </c>
+      <c r="I27">
+        <f>G38/G39</f>
+        <v/>
+      </c>
+      <c r="J27" t="n">
+        <v>34.2372</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>model_tv</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IV = Beginning Book Equity + Σ PV(AE) + PV(TV).|IVPS = IV / Diluted Shares Outstanding.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>scenario_weighted</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Probability-weighted IVPS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SUMPRODUCT of scenario IVPS and probabilities.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>scenario.weighted_ivps</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scenario_Summary</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="I28">
+        <f>SUMPRODUCT(B4:B6,C4:C6)</f>
+        <v/>
+      </c>
+      <c r="J28" t="n">
+        <v>34.0383</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>model_ivps</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>Weighted IVPS = Σ(probability × IVPS) across Bear, Base, Bull.|Probabilities are blue input cells and must sum to 100%.</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
@@ -3405,7 +4701,7 @@
         <f>IF(E19=0,0,-E20/E19)</f>
         <v/>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="22">
         <f>IF(F19=0,0,-F20/F19)</f>
         <v/>
       </c>
@@ -3432,7 +4728,7 @@
         <f>-(E21+E22)</f>
         <v/>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="23">
         <f>-(F21+F22)</f>
         <v/>
       </c>
@@ -3459,34 +4755,34 @@
         <f>E24*(1-E23)</f>
         <v/>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="23">
         <f>F24*(1-F23)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B26" s="23">
+      <c r="B26" s="25">
         <f>B18+B25</f>
         <v/>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="25">
         <f>C18+C25</f>
         <v/>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="25">
         <f>D18+D25</f>
         <v/>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="25">
         <f>E18+E25</f>
         <v/>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="26">
         <f>F18+F25</f>
         <v/>
       </c>
@@ -3521,7 +4817,7 @@
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F29" s="20">
+      <c r="F29" s="23">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",G$6:G$15)</f>
         <v/>
       </c>
@@ -3548,13 +4844,13 @@
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="23">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",G$6:G$15)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>NOWC</t>
         </is>
@@ -3575,7 +4871,7 @@
         <f>E29-E30</f>
         <v/>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="26">
         <f>F29-F30</f>
         <v/>
       </c>
@@ -3602,7 +4898,7 @@
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="23">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",G$6:G$15)</f>
         <v/>
       </c>
@@ -3629,13 +4925,13 @@
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="23">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",G$6:G$15)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>NOLA</t>
         </is>
@@ -3656,13 +4952,13 @@
         <f>E32-E33</f>
         <v/>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="26">
         <f>F32-F33</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
@@ -3683,7 +4979,7 @@
         <f>E31+E34</f>
         <v/>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="26">
         <f>F31+F34</f>
         <v/>
       </c>
@@ -3710,7 +5006,7 @@
         <f>SUMIF($B$6:$B$15,"Financial Asset",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="23">
         <f>SUMIF($B$6:$B$15,"Financial Asset",G$6:G$15)</f>
         <v/>
       </c>
@@ -3737,7 +5033,7 @@
         <f>SUMIF($B$6:$B$15,"Financial Liability",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="23">
         <f>SUMIF($B$6:$B$15,"Financial Liability",G$6:G$15)</f>
         <v/>
       </c>
@@ -3764,7 +5060,7 @@
         <f>E37-E36</f>
         <v/>
       </c>
-      <c r="F38" s="25">
+      <c r="F38" s="23">
         <f>F37-F36</f>
         <v/>
       </c>
@@ -3791,7 +5087,7 @@
         <f>E35-E38</f>
         <v/>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="23">
         <f>F35-F38</f>
         <v/>
       </c>
@@ -3851,7 +5147,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
@@ -3940,7 +5236,7 @@
           <t>RNOA</t>
         </is>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>'Condensed Financials'!F26/(('Condensed Financials'!F35+'Condensed Financials'!E35)/2)</f>
         <v/>
       </c>
@@ -3951,7 +5247,7 @@
           <t>After-tax CoD</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="22">
         <f>'Condensed Financials'!F25/(('Condensed Financials'!F38+'Condensed Financials'!E38)/2)</f>
         <v/>
       </c>
@@ -3962,7 +5258,7 @@
           <t>Spread</t>
         </is>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <f>E5-E6</f>
         <v/>
       </c>
@@ -3973,7 +5269,7 @@
           <t>FLEV</t>
         </is>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="27">
         <f>(('Condensed Financials'!F38+'Condensed Financials'!E38)/2)/(('Condensed Financials'!F39+'Condensed Financials'!E39)/2)</f>
         <v/>
       </c>
@@ -3984,7 +5280,7 @@
           <t>ROE (decomposed)</t>
         </is>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>E5+E8*(E7)</f>
         <v/>
       </c>
@@ -3995,7 +5291,7 @@
           <t>Actual ROE</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="22">
         <f>'Condensed Financials'!F18/(('Condensed Financials'!F39+'Condensed Financials'!E39)/2)</f>
         <v/>
       </c>
@@ -4574,43 +5870,43 @@
           <t>Discount Factor</t>
         </is>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="30">
         <f>1/(1+$B$5)^1</f>
         <v/>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="30">
         <f>1/(1+$B$5)^2</f>
         <v/>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="30">
         <f>1/(1+$B$5)^3</f>
         <v/>
       </c>
-      <c r="J30" s="29">
+      <c r="J30" s="30">
         <f>1/(1+$B$5)^4</f>
         <v/>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="30">
         <f>1/(1+$B$5)^5</f>
         <v/>
       </c>
-      <c r="L30" s="29">
+      <c r="L30" s="30">
         <f>1/(1+$B$5)^6</f>
         <v/>
       </c>
-      <c r="M30" s="29">
+      <c r="M30" s="30">
         <f>1/(1+$B$5)^7</f>
         <v/>
       </c>
-      <c r="N30" s="29">
+      <c r="N30" s="30">
         <f>1/(1+$B$5)^8</f>
         <v/>
       </c>
-      <c r="O30" s="29">
+      <c r="O30" s="30">
         <f>1/(1+$B$5)^9</f>
         <v/>
       </c>
-      <c r="P30" s="29">
+      <c r="P30" s="30">
         <f>1/(1+$B$5)^10</f>
         <v/>
       </c>
@@ -4725,7 +6021,7 @@
           <t>Intrinsic Value per Share</t>
         </is>
       </c>
-      <c r="G40" s="29">
+      <c r="G40" s="30">
         <f>G38/G39</f>
         <v/>
       </c>
@@ -4890,7 +6186,7 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="26">
         <f>'Income Statement'!F7*(1+0.1)</f>
         <v/>
       </c>
@@ -5162,7 +6458,7 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="26">
         <f>G21*G22</f>
         <v/>
       </c>
@@ -5256,7 +6552,7 @@
           <t>Abnormal Earnings</t>
         </is>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="23">
         <f>G28-$B$5*G26</f>
         <v/>
       </c>
@@ -5303,43 +6599,43 @@
           <t>Discount Factor</t>
         </is>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="30">
         <f>1/(1+$B$5)^1</f>
         <v/>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="30">
         <f>1/(1+$B$5)^2</f>
         <v/>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="30">
         <f>1/(1+$B$5)^3</f>
         <v/>
       </c>
-      <c r="J30" s="29">
+      <c r="J30" s="30">
         <f>1/(1+$B$5)^4</f>
         <v/>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="30">
         <f>1/(1+$B$5)^5</f>
         <v/>
       </c>
-      <c r="L30" s="29">
+      <c r="L30" s="30">
         <f>1/(1+$B$5)^6</f>
         <v/>
       </c>
-      <c r="M30" s="29">
+      <c r="M30" s="30">
         <f>1/(1+$B$5)^7</f>
         <v/>
       </c>
-      <c r="N30" s="29">
+      <c r="N30" s="30">
         <f>1/(1+$B$5)^8</f>
         <v/>
       </c>
-      <c r="O30" s="29">
+      <c r="O30" s="30">
         <f>1/(1+$B$5)^9</f>
         <v/>
       </c>
-      <c r="P30" s="29">
+      <c r="P30" s="30">
         <f>1/(1+$B$5)^10</f>
         <v/>
       </c>
@@ -5422,7 +6718,7 @@
           <t>PV Terminal Value</t>
         </is>
       </c>
-      <c r="G37" s="25">
+      <c r="G37" s="23">
         <f>P36*P30</f>
         <v/>
       </c>
@@ -5454,7 +6750,7 @@
           <t>Intrinsic Value per Share</t>
         </is>
       </c>
-      <c r="G40" s="30">
+      <c r="G40" s="31">
         <f>G38/G39</f>
         <v/>
       </c>
@@ -6033,43 +7329,43 @@
           <t>Discount Factor</t>
         </is>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="30">
         <f>1/(1+$B$5)^1</f>
         <v/>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="30">
         <f>1/(1+$B$5)^2</f>
         <v/>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="30">
         <f>1/(1+$B$5)^3</f>
         <v/>
       </c>
-      <c r="J30" s="29">
+      <c r="J30" s="30">
         <f>1/(1+$B$5)^4</f>
         <v/>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="30">
         <f>1/(1+$B$5)^5</f>
         <v/>
       </c>
-      <c r="L30" s="29">
+      <c r="L30" s="30">
         <f>1/(1+$B$5)^6</f>
         <v/>
       </c>
-      <c r="M30" s="29">
+      <c r="M30" s="30">
         <f>1/(1+$B$5)^7</f>
         <v/>
       </c>
-      <c r="N30" s="29">
+      <c r="N30" s="30">
         <f>1/(1+$B$5)^8</f>
         <v/>
       </c>
-      <c r="O30" s="29">
+      <c r="O30" s="30">
         <f>1/(1+$B$5)^9</f>
         <v/>
       </c>
-      <c r="P30" s="29">
+      <c r="P30" s="30">
         <f>1/(1+$B$5)^10</f>
         <v/>
       </c>
@@ -6184,7 +7480,7 @@
           <t>Intrinsic Value per Share</t>
         </is>
       </c>
-      <c r="G40" s="29">
+      <c r="G40" s="30">
         <f>G38/G39</f>
         <v/>
       </c>

--- a/example/DEMO_HK_Answer_Key.xlsx
+++ b/example/DEMO_HK_Answer_Key.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condensed Financials" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALT DuPont" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Bear" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Base" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Bull" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario_Summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Bear" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Base" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Bull" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario_Summary" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ComponentMap" sheetId="11" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames/>
@@ -26,13 +26,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mmm dd, yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0)"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,9 +43,6 @@
       <b val="1"/>
     </font>
     <font/>
-    <font>
-      <color rgb="000000FF"/>
-    </font>
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
@@ -119,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,32 +124,23 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -349,56 +336,6 @@
     <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <t>Relate net income to average reformulated equity.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>BAV Trainer</author>
-  </authors>
-  <commentList>
-    <comment ref="G21" authorId="0" shapeId="0">
-      <text>
-        <t>Anchor revenue × (1 + Y1 growth).</t>
-      </text>
-    </comment>
-    <comment ref="G27" authorId="0" shapeId="0">
-      <text>
-        <t>Forecast sales × NOPAT margin.</t>
-      </text>
-    </comment>
-    <comment ref="G29" authorId="0" shapeId="0">
-      <text>
-        <t>Residual income: NI − Ke × Equity.</t>
-      </text>
-    </comment>
-    <comment ref="G37" authorId="0" shapeId="0">
-      <text>
-        <t>Gordon growth on terminal-year abnormal earnings, discounted.</t>
-      </text>
-    </comment>
-    <comment ref="G40" authorId="0" shapeId="0">
-      <text>
-        <t>Book equity + PV(abnormal earnings) + PV(terminal value).</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>BAV Trainer</author>
-  </authors>
-  <commentList>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t>SUMPRODUCT of scenario IVPS and probabilities.</t>
       </text>
     </comment>
   </commentList>
@@ -694,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -705,718 +642,568 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>BAV Excel Trainer</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Complete yellow practice cells in dependency order. Run Check to validate the whole workbook: blank cells stay yellow, correct cells turn green, and incorrect cells turn red. Open the matching Answer Key for the formula/input and Note hint.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Tab</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Cell</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Depends on</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Effective tax rate (latest fiscal year)</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>F23</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Net interest (latest fiscal year)</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>F24</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Net interest after tax</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>F25</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>effective_tax_rate_fy, net_interest_fy</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>NOPAT (latest fiscal year)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>F26</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>net_interest_after_tax_fy</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Operating working capital assets</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>F29</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Operating working capital liabilities</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>F30</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Net Operating Working Capital (NOWC)</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>F31</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>owca_agg, owcl_agg</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Operating long-term assets</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>F32</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Operating long-term liabilities</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>F33</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Net operating long-term assets (NOLA)</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>F34</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>olta_agg, oltl_agg</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Net Operating Assets (NOA)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>F35</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>nowc_agg, nola_agg</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Financial assets</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>F36</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Financial liabilities</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>F37</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>F38</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>financial_assets_agg, financial_liabilities_agg</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Reformulated equity</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>F39</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>noa_agg, net_debt</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Return on Net Operating Assets (RNOA)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>E5</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>nopat_fy, noa_agg</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>E6</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>net_interest_after_tax_fy, net_debt</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Operating Spread (RNOA − After-tax CoD)</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>E7</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>rnoa, after_tax_cod</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Financial leverage (FLEV)</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>E8</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>net_debt, equity_reformulated_fy</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>ROE decomposition</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>E9</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>rnoa, spread, flev</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Actual ROE</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>E10</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>equity_reformulated_fy</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>Base case Y1 revenue forecast</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>Model_Base</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>G21</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>nopat_fy</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>Base case Y1 NOPAT</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>Model_Base</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>G27</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>model_sales_y1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Year 1 abnormal earnings</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>Model_Base</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>G29</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>model_nopat_y1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Terminal value (PV of abnormal earnings)</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>Model_Base</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>G37</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>model_ae_y1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Intrinsic value per share</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>Model_Base</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>G40</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>model_tv</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Probability-weighted IVPS</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Scenario_Summary</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>E8</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>model_ivps</t>
         </is>
       </c>
     </row>
@@ -1431,93 +1218,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Demo Holdings Limited — Scenario Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>IVPS</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="n"/>
-      <c r="E3" s="32" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="B4" s="33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C4" s="14">
-        <f>'Model_Bear'!G40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="B5" s="33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C5" s="14">
-        <f>'Model_Base'!G40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C6" s="14">
-        <f>'Model_Bull'!G40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>Weighted IVPS</t>
-        </is>
-      </c>
-      <c r="E8" s="29">
-        <f>SUMPRODUCT(B4:B6,C4:C6)</f>
-        <v/>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Deferred from historical-only v1</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1527,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2927,396 +2639,6 @@
         </is>
       </c>
       <c r="O22" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>model_sales_y1</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>22</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Base case Y1 revenue forecast</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Anchor revenue × (1 + Y1 growth).</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>model.sales.y1</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>forecasting</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Model_Base</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>G21</t>
-        </is>
-      </c>
-      <c r="I23">
-        <f>'Income Statement'!F7*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="J23" t="n">
-        <v>13750</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>nopat_fy</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Y1 beginning sales = prior fiscal year revenue from Income Statement.|Y1 Sales = Anchor Revenue × (1 + growthVector[0]).</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>model_nopat_y1</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>23</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Base case Y1 NOPAT</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Forecast sales × NOPAT margin.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>model.nopat.y1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>forecasting</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Model_Base</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>G27</t>
-        </is>
-      </c>
-      <c r="I24">
-        <f>G21*G22</f>
-        <v/>
-      </c>
-      <c r="J24" t="n">
-        <v>2062.5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>model_sales_y1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>NOPAT = Sales × marginVector[t].|Margin vector is a blue forecast input.</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>model_ae_y1</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>24</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Year 1 abnormal earnings</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Residual income: NI − Ke × Equity.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>model.abnormal_earnings.y1</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Model_Base</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>G29</t>
-        </is>
-      </c>
-      <c r="I25">
-        <f>G28-$B$5*G26</f>
-        <v/>
-      </c>
-      <c r="J25" t="n">
-        <v>1043.756153868829</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>model_nopat_y1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Net Income = NOPAT − Net Debt × after-tax cost of debt.|Abnormal Earnings = Net Income − Cost of Equity × Book Equity.</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>model_tv</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>25</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Terminal value (PV of abnormal earnings)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Gordon growth on terminal-year abnormal earnings, discounted.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>model.terminal_value.pv</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Model_Base</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>G37</t>
-        </is>
-      </c>
-      <c r="I26">
-        <f>P36*P30</f>
-        <v/>
-      </c>
-      <c r="J26" t="n">
-        <v>15516.94169433467</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>model_ae_y1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>TV = AE₁₀ × (1 + g) / (Ke − g).|Discount TV back 10 years at Ke.</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>model_ivps</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>26</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Intrinsic value per share</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Book equity + PV(abnormal earnings) + PV(terminal value).</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>model.ivps</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Model_Base</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>G40</t>
-        </is>
-      </c>
-      <c r="I27">
-        <f>G38/G39</f>
-        <v/>
-      </c>
-      <c r="J27" t="n">
-        <v>34.2372</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>model_tv</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>IV = Beginning Book Equity + Σ PV(AE) + PV(TV).|IVPS = IV / Diluted Shares Outstanding.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>scenario_weighted</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Probability-weighted IVPS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SUMPRODUCT of scenario IVPS and probabilities.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>scenario.weighted_ivps</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Scenario_Summary</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>E8</t>
-        </is>
-      </c>
-      <c r="I28">
-        <f>SUMPRODUCT(B4:B6,C4:C6)</f>
-        <v/>
-      </c>
-      <c r="J28" t="n">
-        <v>34.0383</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>model_ivps</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Weighted IVPS = Σ(probability × IVPS) across Bear, Base, Bull.|Probabilities are blue input cells and must sum to 100%.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
@@ -3345,28 +2667,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Company: Demo Holdings Limited (DEMO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Statement: Income Statement</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Units: HKD in Millions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Source: manual ingestion (HK)</t>
         </is>
@@ -3374,244 +2696,244 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="13" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="14" t="n">
         <v>8500</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="14" t="n">
         <v>9200</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="14" t="n">
         <v>10100</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="14" t="n">
         <v>11200</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="14" t="n">
         <v>12500</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Cost of sales</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="15" t="n">
         <v>-3400</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="15" t="n">
         <v>-3680</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="15" t="n">
         <v>-4040</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="15" t="n">
         <v>-4480</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="15" t="n">
         <v>-5000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="15" t="n">
         <v>5100</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="15" t="n">
         <v>5520</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="15" t="n">
         <v>6060</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="15" t="n">
         <v>6720</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="15" t="n">
         <v>7500</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Administrative expenses</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="15" t="n">
         <v>-1700</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="15" t="n">
         <v>-1840</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="15" t="n">
         <v>-2020</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="15" t="n">
         <v>-2240</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="15" t="n">
         <v>-2500</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Operating profit</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="15" t="n">
         <v>3400</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="15" t="n">
         <v>3680</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="15" t="n">
         <v>4040</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="15" t="n">
         <v>4480</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="15" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Finance costs</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="15" t="n">
         <v>-120</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="15" t="n">
         <v>-130</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="15" t="n">
         <v>-140</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="15" t="n">
         <v>-150</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="15" t="n">
         <v>-160</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Finance income</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="15" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="15" t="n">
         <v>3325</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="15" t="n">
         <v>3600</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="15" t="n">
         <v>3955</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="15" t="n">
         <v>4390</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="15" t="n">
         <v>4905</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Income tax expense</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="15" t="n">
         <v>-565</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="15" t="n">
         <v>-612</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="15" t="n">
         <v>-672</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="15" t="n">
         <v>-746</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="15" t="n">
         <v>-833</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="15" t="n">
         <v>2760</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="15" t="n">
         <v>2988</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="15" t="n">
         <v>3283</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="15" t="n">
         <v>3644</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="15" t="n">
         <v>4072</v>
       </c>
     </row>
@@ -3638,28 +2960,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Company: Demo Holdings Limited (DEMO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Statement: Balance Sheet</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Units: HKD in Millions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Source: manual ingestion (HK)</t>
         </is>
@@ -3667,310 +2989,310 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="13" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="15" t="n">
         <v>1350</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="15" t="n">
         <v>1680</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="15" t="n">
         <v>1850</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Trade receivables</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="15" t="n">
         <v>850</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="15" t="n">
         <v>920</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="15" t="n">
         <v>1010</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="15" t="n">
         <v>1120</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="15" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="14" t="n">
         <v>680</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="14" t="n">
         <v>736</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="14" t="n">
         <v>808</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="14" t="n">
         <v>896</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="14" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="15" t="n">
         <v>3200</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="15" t="n">
         <v>3400</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="15" t="n">
         <v>3600</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="15" t="n">
         <v>3800</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="15" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="14" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Other non-current assets</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="15" t="n">
         <v>1670</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="15" t="n">
         <v>1894</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="15" t="n">
         <v>2282</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="15" t="n">
         <v>2804</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="15" t="n">
         <v>3500</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="15" t="n">
         <v>8500</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="15" t="n">
         <v>9200</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="15" t="n">
         <v>10100</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="15" t="n">
         <v>11200</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="15" t="n">
         <v>12500</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Trade payables</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="15" t="n">
         <v>595</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="15" t="n">
         <v>644</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="15" t="n">
         <v>707</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="15" t="n">
         <v>784</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="15" t="n">
         <v>875</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Bank borrowings</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="15" t="n">
         <v>1400</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="15" t="n">
         <v>1300</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="15" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Other non-current liabilities</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="15" t="n">
         <v>1305</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="15" t="n">
         <v>1456</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="15" t="n">
         <v>1593</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="15" t="n">
         <v>1716</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="15" t="n">
         <v>1825</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="15" t="n">
         <v>3400</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="D17" s="20" t="n">
+      <c r="D17" s="15" t="n">
         <v>3600</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="15" t="n">
         <v>3700</v>
       </c>
-      <c r="F17" s="20" t="n">
+      <c r="F17" s="15" t="n">
         <v>3800</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Share capital and reserves</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="15" t="n">
         <v>5100</v>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="15" t="n">
         <v>5700</v>
       </c>
-      <c r="D18" s="20" t="n">
+      <c r="D18" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="E18" s="20" t="n">
+      <c r="E18" s="15" t="n">
         <v>7500</v>
       </c>
-      <c r="F18" s="20" t="n">
+      <c r="F18" s="15" t="n">
         <v>8700</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="15" t="n">
         <v>5100</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="15" t="n">
         <v>5700</v>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="E19" s="20" t="n">
+      <c r="E19" s="15" t="n">
         <v>7500</v>
       </c>
-      <c r="F19" s="20" t="n">
+      <c r="F19" s="15" t="n">
         <v>8700</v>
       </c>
     </row>
@@ -3997,28 +3319,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Company: Demo Holdings Limited (DEMO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Statement: Cash Flow Statement</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Units: HKD in Millions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Source: manual ingestion (HK)</t>
         </is>
@@ -4026,156 +3348,156 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="13" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="15" t="n">
         <v>2760</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="15" t="n">
         <v>2988</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="15" t="n">
         <v>3283</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="15" t="n">
         <v>3644</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="15" t="n">
         <v>4072</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="15" t="n">
         <v>340</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="15" t="n">
         <v>368</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="15" t="n">
         <v>404</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="15" t="n">
         <v>448</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="15" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="15" t="n">
         <v>1450</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="15" t="n">
         <v>1600</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="15" t="n">
         <v>1750</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="15" t="n">
         <v>1930</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="15" t="n">
         <v>2070</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Net cash used in investing activities</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="15" t="n">
         <v>-800</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="15" t="n">
         <v>-850</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="15" t="n">
         <v>-900</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="15" t="n">
         <v>-950</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="15" t="n">
         <v>-1000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Net cash from financing activities</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="15" t="n">
         <v>-500</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="15" t="n">
         <v>-600</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="15" t="n">
         <v>-700</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="15" t="n">
         <v>-800</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="15" t="n">
         <v>-900</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Net change in cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="15" t="n">
         <v>180</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="15" t="n">
         <v>170</v>
       </c>
     </row>
@@ -4204,7 +3526,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Demo Holdings Limited (DEMO) — Condensed Financials</t>
         </is>
@@ -4213,962 +3535,962 @@
     <row r="2"/>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>BALANCE SHEET CLASSIFICATION</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="13" t="n">
         <v>46022</v>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Financial Asset</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="15" t="n">
         <v>1350</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="15" t="n">
         <v>1680</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="15" t="n">
         <v>1850</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Trade receivables</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Operating Working Capital Asset</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="15" t="n">
         <v>850</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="15" t="n">
         <v>920</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="15" t="n">
         <v>1010</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="15" t="n">
         <v>1120</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="15" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Operating Working Capital Asset</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="14" t="n">
         <v>680</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="14" t="n">
         <v>736</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="14" t="n">
         <v>808</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="14" t="n">
         <v>896</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="14" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Operating Long-Term Asset</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="15" t="n">
         <v>3200</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="15" t="n">
         <v>3400</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="15" t="n">
         <v>3600</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="15" t="n">
         <v>3800</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="15" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Operating Long-Term Asset</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="14" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Other non-current assets</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Operating Long-Term Asset</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="15" t="n">
         <v>1670</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="15" t="n">
         <v>1894</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="15" t="n">
         <v>2282</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="15" t="n">
         <v>2804</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="15" t="n">
         <v>3500</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Trade payables</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Operating Working Capital Liability</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="15" t="n">
         <v>595</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="15" t="n">
         <v>644</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="15" t="n">
         <v>707</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="15" t="n">
         <v>784</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="15" t="n">
         <v>875</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Bank borrowings</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Financial Liability</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="15" t="n">
         <v>1400</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="15" t="n">
         <v>1300</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="15" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Other non-current liabilities</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Operating Long-Term Liability</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="15" t="n">
         <v>1305</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="15" t="n">
         <v>1456</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="15" t="n">
         <v>1593</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="15" t="n">
         <v>1716</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="15" t="n">
         <v>1825</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Share capital and reserves</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="15" t="n">
         <v>5100</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="15" t="n">
         <v>5700</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="15" t="n">
         <v>7500</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="15" t="n">
         <v>8700</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>CONDENSED INCOME STATEMENT</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="13" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="12">
         <f>'Income Statement'!B16</f>
         <v/>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="12">
         <f>'Income Statement'!C16</f>
         <v/>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="12">
         <f>'Income Statement'!D16</f>
         <v/>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="12">
         <f>'Income Statement'!E16</f>
         <v/>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="12">
         <f>'Income Statement'!F16</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="12">
         <f>'Income Statement'!B14</f>
         <v/>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="12">
         <f>'Income Statement'!C14</f>
         <v/>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="12">
         <f>'Income Statement'!D14</f>
         <v/>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="12">
         <f>'Income Statement'!E14</f>
         <v/>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="12">
         <f>'Income Statement'!F14</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Tax Expense</t>
         </is>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="12">
         <f>'Income Statement'!B15</f>
         <v/>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="12">
         <f>'Income Statement'!C15</f>
         <v/>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="12">
         <f>'Income Statement'!D15</f>
         <v/>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="12">
         <f>'Income Statement'!E15</f>
         <v/>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="12">
         <f>'Income Statement'!F15</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="12">
         <f>'Income Statement'!B12</f>
         <v/>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="12">
         <f>'Income Statement'!C12</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="12">
         <f>'Income Statement'!D12</f>
         <v/>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="12">
         <f>'Income Statement'!E12</f>
         <v/>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="12">
         <f>'Income Statement'!F12</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="12">
         <f>'Income Statement'!B13</f>
         <v/>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="12">
         <f>'Income Statement'!C13</f>
         <v/>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="12">
         <f>'Income Statement'!D13</f>
         <v/>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="12">
         <f>'Income Statement'!E13</f>
         <v/>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="12">
         <f>'Income Statement'!F13</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Effective Tax Rate</t>
         </is>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="16">
         <f>IF(B19=0,0,-B20/B19)</f>
         <v/>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="16">
         <f>IF(C19=0,0,-C20/C19)</f>
         <v/>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="16">
         <f>IF(D19=0,0,-D20/D19)</f>
         <v/>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="16">
         <f>IF(E19=0,0,-E20/E19)</f>
         <v/>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="17">
         <f>IF(F19=0,0,-F20/F19)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Net Interest</t>
         </is>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="15">
         <f>-(B21+B22)</f>
         <v/>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="15">
         <f>-(C21+C22)</f>
         <v/>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="15">
         <f>-(D21+D22)</f>
         <v/>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="15">
         <f>-(E21+E22)</f>
         <v/>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="18">
         <f>-(F21+F22)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Net Interest After Tax</t>
         </is>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="15">
         <f>B24*(1-B23)</f>
         <v/>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="15">
         <f>C24*(1-C23)</f>
         <v/>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="15">
         <f>D24*(1-D23)</f>
         <v/>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="15">
         <f>E24*(1-E23)</f>
         <v/>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="18">
         <f>F24*(1-F23)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="20">
         <f>B18+B25</f>
         <v/>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="20">
         <f>C18+C25</f>
         <v/>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="20">
         <f>D18+D25</f>
         <v/>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="20">
         <f>E18+E25</f>
         <v/>
       </c>
-      <c r="F26" s="26">
+      <c r="F26" s="21">
         <f>F18+F25</f>
         <v/>
       </c>
     </row>
     <row r="27"/>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>CONDENSED BALANCE SHEET</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Operating Working Capital Assets</t>
         </is>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",C$6:C$15)</f>
         <v/>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",D$6:D$15)</f>
         <v/>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",E$6:E$15)</f>
         <v/>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="18">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",G$6:G$15)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Operating Working Capital Liabilities</t>
         </is>
       </c>
-      <c r="B30" s="20">
+      <c r="B30" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",C$6:C$15)</f>
         <v/>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",D$6:D$15)</f>
         <v/>
       </c>
-      <c r="D30" s="20">
+      <c r="D30" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",E$6:E$15)</f>
         <v/>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="18">
         <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",G$6:G$15)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>NOWC</t>
         </is>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="14">
         <f>B29-B30</f>
         <v/>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="14">
         <f>C29-C30</f>
         <v/>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="14">
         <f>D29-D30</f>
         <v/>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="14">
         <f>E29-E30</f>
         <v/>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="21">
         <f>F29-F30</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Operating Long-Term Assets</t>
         </is>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",C$6:C$15)</f>
         <v/>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",D$6:D$15)</f>
         <v/>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",E$6:E$15)</f>
         <v/>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="18">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",G$6:G$15)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Operating Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B33" s="20">
+      <c r="B33" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",C$6:C$15)</f>
         <v/>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",D$6:D$15)</f>
         <v/>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",E$6:E$15)</f>
         <v/>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="15">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="18">
         <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",G$6:G$15)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>NOLA</t>
         </is>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="14">
         <f>B32-B33</f>
         <v/>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="14">
         <f>C32-C33</f>
         <v/>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="14">
         <f>D32-D33</f>
         <v/>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="14">
         <f>E32-E33</f>
         <v/>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="21">
         <f>F32-F33</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="B35" s="19">
+      <c r="B35" s="14">
         <f>B31+B34</f>
         <v/>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="14">
         <f>C31+C34</f>
         <v/>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="14">
         <f>D31+D34</f>
         <v/>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="14">
         <f>E31+E34</f>
         <v/>
       </c>
-      <c r="F35" s="26">
+      <c r="F35" s="21">
         <f>F31+F34</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Financial Assets</t>
         </is>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="15">
         <f>SUMIF($B$6:$B$15,"Financial Asset",C$6:C$15)</f>
         <v/>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="15">
         <f>SUMIF($B$6:$B$15,"Financial Asset",D$6:D$15)</f>
         <v/>
       </c>
-      <c r="D36" s="20">
+      <c r="D36" s="15">
         <f>SUMIF($B$6:$B$15,"Financial Asset",E$6:E$15)</f>
         <v/>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="15">
         <f>SUMIF($B$6:$B$15,"Financial Asset",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="18">
         <f>SUMIF($B$6:$B$15,"Financial Asset",G$6:G$15)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Financial Liabilities</t>
         </is>
       </c>
-      <c r="B37" s="20">
+      <c r="B37" s="15">
         <f>SUMIF($B$6:$B$15,"Financial Liability",C$6:C$15)</f>
         <v/>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="15">
         <f>SUMIF($B$6:$B$15,"Financial Liability",D$6:D$15)</f>
         <v/>
       </c>
-      <c r="D37" s="20">
+      <c r="D37" s="15">
         <f>SUMIF($B$6:$B$15,"Financial Liability",E$6:E$15)</f>
         <v/>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="15">
         <f>SUMIF($B$6:$B$15,"Financial Liability",F$6:F$15)</f>
         <v/>
       </c>
-      <c r="F37" s="23">
+      <c r="F37" s="18">
         <f>SUMIF($B$6:$B$15,"Financial Liability",G$6:G$15)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="15">
         <f>B37-B36</f>
         <v/>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="15">
         <f>C37-C36</f>
         <v/>
       </c>
-      <c r="D38" s="20">
+      <c r="D38" s="15">
         <f>D37-D36</f>
         <v/>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="15">
         <f>E37-E36</f>
         <v/>
       </c>
-      <c r="F38" s="23">
+      <c r="F38" s="18">
         <f>F37-F36</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Equity (NOA - Net Debt)</t>
         </is>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="15">
         <f>B35-B38</f>
         <v/>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="15">
         <f>C35-C38</f>
         <v/>
       </c>
-      <c r="D39" s="20">
+      <c r="D39" s="15">
         <f>D35-D38</f>
         <v/>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="15">
         <f>E35-E38</f>
         <v/>
       </c>
-      <c r="F39" s="23">
+      <c r="F39" s="18">
         <f>F35-F38</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Reported Equity</t>
         </is>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="15">
         <f>'Balance Sheet'!B19</f>
         <v/>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="15">
         <f>'Balance Sheet'!C19</f>
         <v/>
       </c>
-      <c r="D40" s="20">
+      <c r="D40" s="15">
         <f>'Balance Sheet'!D19</f>
         <v/>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="15">
         <f>'Balance Sheet'!E19</f>
         <v/>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="15">
         <f>'Balance Sheet'!F19</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Total Capital</t>
         </is>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="15">
         <f>B38+B39</f>
         <v/>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="15">
         <f>C38+C39</f>
         <v/>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="15">
         <f>D38+D39</f>
         <v/>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="15">
         <f>E38+E39</f>
         <v/>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="15">
         <f>F38+F39</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
       </c>
-      <c r="B42" s="14">
+      <c r="B42" s="9">
         <f>IF(ABS(B39-B40)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="9">
         <f>IF(ABS(C39-C40)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="9">
         <f>IF(ABS(D39-D40)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="9">
         <f>IF(ABS(E39-E40)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="F42" s="14">
+      <c r="F42" s="9">
         <f>IF(ABS(F39-F40)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
@@ -5197,14 +4519,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Demo Holdings Limited — DuPont Decomposition</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>ROE = RNOA + FLEV × Spread</t>
         </is>
@@ -5212,86 +4534,86 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
+      <c r="B4" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="C4" s="18" t="n">
+      <c r="C4" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="13" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>RNOA</t>
         </is>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="22">
         <f>'Condensed Financials'!F26/(('Condensed Financials'!F35+'Condensed Financials'!E35)/2)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>After-tax CoD</t>
         </is>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="17">
         <f>'Condensed Financials'!F25/(('Condensed Financials'!F38+'Condensed Financials'!E38)/2)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="23">
         <f>E5-E6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>FLEV</t>
         </is>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="22">
         <f>(('Condensed Financials'!F38+'Condensed Financials'!E38)/2)/(('Condensed Financials'!F39+'Condensed Financials'!E39)/2)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>ROE (decomposed)</t>
         </is>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="24">
         <f>E5+E8*(E7)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Actual ROE</t>
         </is>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="17">
         <f>'Condensed Financials'!F18/(('Condensed Financials'!F39+'Condensed Financials'!E39)/2)</f>
         <v/>
       </c>
@@ -5308,722 +4630,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Demo Holdings Limited — Bear Scenario</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Cost of Equity (Ke)</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="n">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n">
-        <v>0.165</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>After-tax CoD</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n">
-        <v>-0.2273251281748943</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>Financial leverage</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n">
-        <v>-0.09433962264150944</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Terminal growth (g)</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>FORECAST BLOCK</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="L20" s="15" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
-      </c>
-      <c r="M20" s="15" t="inlineStr">
-        <is>
-          <t>Y7</t>
-        </is>
-      </c>
-      <c r="N20" s="15" t="inlineStr">
-        <is>
-          <t>Y8</t>
-        </is>
-      </c>
-      <c r="O20" s="15" t="inlineStr">
-        <is>
-          <t>Y9</t>
-        </is>
-      </c>
-      <c r="P20" s="15" t="inlineStr">
-        <is>
-          <t>Y10</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="G21" s="19">
-        <f>'Income Statement'!F7*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="H21" s="19">
-        <f>G21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="I21" s="19">
-        <f>H21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="J21" s="19">
-        <f>I21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="K21" s="19">
-        <f>J21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="L21" s="19">
-        <f>K21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="M21" s="19">
-        <f>L21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="N21" s="19">
-        <f>M21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="O21" s="19">
-        <f>N21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="P21" s="19">
-        <f>O21*(1+0.1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>NOPAT Margin</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>NOWC</t>
-        </is>
-      </c>
-      <c r="G23" s="19">
-        <f>'Condensed Financials'!F31</f>
-        <v/>
-      </c>
-      <c r="H23" s="19">
-        <f>H21*0.05</f>
-        <v/>
-      </c>
-      <c r="I23" s="19">
-        <f>I21*0.05</f>
-        <v/>
-      </c>
-      <c r="J23" s="19">
-        <f>J21*0.05</f>
-        <v/>
-      </c>
-      <c r="K23" s="19">
-        <f>K21*0.05</f>
-        <v/>
-      </c>
-      <c r="L23" s="19">
-        <f>L21*0.05</f>
-        <v/>
-      </c>
-      <c r="M23" s="19">
-        <f>M21*0.05</f>
-        <v/>
-      </c>
-      <c r="N23" s="19">
-        <f>N21*0.05</f>
-        <v/>
-      </c>
-      <c r="O23" s="19">
-        <f>O21*0.05</f>
-        <v/>
-      </c>
-      <c r="P23" s="19">
-        <f>P21*0.05</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>NOLA</t>
-        </is>
-      </c>
-      <c r="G24" s="19">
-        <f>'Condensed Financials'!F35-'Condensed Financials'!F31</f>
-        <v/>
-      </c>
-      <c r="H24" s="19">
-        <f>H21*0.5</f>
-        <v/>
-      </c>
-      <c r="I24" s="19">
-        <f>I21*0.5</f>
-        <v/>
-      </c>
-      <c r="J24" s="19">
-        <f>J21*0.5</f>
-        <v/>
-      </c>
-      <c r="K24" s="19">
-        <f>K21*0.5</f>
-        <v/>
-      </c>
-      <c r="L24" s="19">
-        <f>L21*0.5</f>
-        <v/>
-      </c>
-      <c r="M24" s="19">
-        <f>M21*0.5</f>
-        <v/>
-      </c>
-      <c r="N24" s="19">
-        <f>N21*0.5</f>
-        <v/>
-      </c>
-      <c r="O24" s="19">
-        <f>O21*0.5</f>
-        <v/>
-      </c>
-      <c r="P24" s="19">
-        <f>P21*0.5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>Net Debt</t>
-        </is>
-      </c>
-      <c r="G25" s="20">
-        <f>'Condensed Financials'!F38</f>
-        <v/>
-      </c>
-      <c r="H25" s="20">
-        <f>($B$8)*(H23+H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="20">
-        <f>($B$8)*(I23+I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="20">
-        <f>($B$8)*(J23+J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="20">
-        <f>($B$8)*(K23+K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="20">
-        <f>($B$8)*(L23+L24)</f>
-        <v/>
-      </c>
-      <c r="M25" s="20">
-        <f>($B$8)*(M23+M24)</f>
-        <v/>
-      </c>
-      <c r="N25" s="20">
-        <f>($B$8)*(N23+N24)</f>
-        <v/>
-      </c>
-      <c r="O25" s="20">
-        <f>($B$8)*(O23+O24)</f>
-        <v/>
-      </c>
-      <c r="P25" s="20">
-        <f>($B$8)*(P23+P24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>Book Equity</t>
-        </is>
-      </c>
-      <c r="G26" s="20">
-        <f>G23+G24-G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="20">
-        <f>H23+H24-H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="20">
-        <f>I23+I24-I25</f>
-        <v/>
-      </c>
-      <c r="J26" s="20">
-        <f>J23+J24-J25</f>
-        <v/>
-      </c>
-      <c r="K26" s="20">
-        <f>K23+K24-K25</f>
-        <v/>
-      </c>
-      <c r="L26" s="20">
-        <f>L23+L24-L25</f>
-        <v/>
-      </c>
-      <c r="M26" s="20">
-        <f>M23+M24-M25</f>
-        <v/>
-      </c>
-      <c r="N26" s="20">
-        <f>N23+N24-N25</f>
-        <v/>
-      </c>
-      <c r="O26" s="20">
-        <f>O23+O24-O25</f>
-        <v/>
-      </c>
-      <c r="P26" s="20">
-        <f>P23+P24-P25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>NOPAT</t>
-        </is>
-      </c>
-      <c r="G27" s="19">
-        <f>G21*G22</f>
-        <v/>
-      </c>
-      <c r="H27" s="19">
-        <f>H21*H22</f>
-        <v/>
-      </c>
-      <c r="I27" s="19">
-        <f>I21*I22</f>
-        <v/>
-      </c>
-      <c r="J27" s="19">
-        <f>J21*J22</f>
-        <v/>
-      </c>
-      <c r="K27" s="19">
-        <f>K21*K22</f>
-        <v/>
-      </c>
-      <c r="L27" s="19">
-        <f>L21*L22</f>
-        <v/>
-      </c>
-      <c r="M27" s="19">
-        <f>M21*M22</f>
-        <v/>
-      </c>
-      <c r="N27" s="19">
-        <f>N21*N22</f>
-        <v/>
-      </c>
-      <c r="O27" s="19">
-        <f>O21*O22</f>
-        <v/>
-      </c>
-      <c r="P27" s="19">
-        <f>P21*P22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="G28" s="20">
-        <f>G27-G25*$B$7</f>
-        <v/>
-      </c>
-      <c r="H28" s="20">
-        <f>H27-H25*$B$7</f>
-        <v/>
-      </c>
-      <c r="I28" s="20">
-        <f>I27-I25*$B$7</f>
-        <v/>
-      </c>
-      <c r="J28" s="20">
-        <f>J27-J25*$B$7</f>
-        <v/>
-      </c>
-      <c r="K28" s="20">
-        <f>K27-K25*$B$7</f>
-        <v/>
-      </c>
-      <c r="L28" s="20">
-        <f>L27-L25*$B$7</f>
-        <v/>
-      </c>
-      <c r="M28" s="20">
-        <f>M27-M25*$B$7</f>
-        <v/>
-      </c>
-      <c r="N28" s="20">
-        <f>N27-N25*$B$7</f>
-        <v/>
-      </c>
-      <c r="O28" s="20">
-        <f>O27-O25*$B$7</f>
-        <v/>
-      </c>
-      <c r="P28" s="20">
-        <f>P27-P25*$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Abnormal Earnings</t>
-        </is>
-      </c>
-      <c r="G29" s="20">
-        <f>G28-$B$5*G26</f>
-        <v/>
-      </c>
-      <c r="H29" s="20">
-        <f>H28-$B$5*H26</f>
-        <v/>
-      </c>
-      <c r="I29" s="20">
-        <f>I28-$B$5*I26</f>
-        <v/>
-      </c>
-      <c r="J29" s="20">
-        <f>J28-$B$5*J26</f>
-        <v/>
-      </c>
-      <c r="K29" s="20">
-        <f>K28-$B$5*K26</f>
-        <v/>
-      </c>
-      <c r="L29" s="20">
-        <f>L28-$B$5*L26</f>
-        <v/>
-      </c>
-      <c r="M29" s="20">
-        <f>M28-$B$5*M26</f>
-        <v/>
-      </c>
-      <c r="N29" s="20">
-        <f>N28-$B$5*N26</f>
-        <v/>
-      </c>
-      <c r="O29" s="20">
-        <f>O28-$B$5*O26</f>
-        <v/>
-      </c>
-      <c r="P29" s="20">
-        <f>P28-$B$5*P26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Discount Factor</t>
-        </is>
-      </c>
-      <c r="G30" s="30">
-        <f>1/(1+$B$5)^1</f>
-        <v/>
-      </c>
-      <c r="H30" s="30">
-        <f>1/(1+$B$5)^2</f>
-        <v/>
-      </c>
-      <c r="I30" s="30">
-        <f>1/(1+$B$5)^3</f>
-        <v/>
-      </c>
-      <c r="J30" s="30">
-        <f>1/(1+$B$5)^4</f>
-        <v/>
-      </c>
-      <c r="K30" s="30">
-        <f>1/(1+$B$5)^5</f>
-        <v/>
-      </c>
-      <c r="L30" s="30">
-        <f>1/(1+$B$5)^6</f>
-        <v/>
-      </c>
-      <c r="M30" s="30">
-        <f>1/(1+$B$5)^7</f>
-        <v/>
-      </c>
-      <c r="N30" s="30">
-        <f>1/(1+$B$5)^8</f>
-        <v/>
-      </c>
-      <c r="O30" s="30">
-        <f>1/(1+$B$5)^9</f>
-        <v/>
-      </c>
-      <c r="P30" s="30">
-        <f>1/(1+$B$5)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>PV Abnormal Earnings</t>
-        </is>
-      </c>
-      <c r="G31" s="20">
-        <f>G29*G30</f>
-        <v/>
-      </c>
-      <c r="H31" s="20">
-        <f>H29*H30</f>
-        <v/>
-      </c>
-      <c r="I31" s="20">
-        <f>I29*I30</f>
-        <v/>
-      </c>
-      <c r="J31" s="20">
-        <f>J29*J30</f>
-        <v/>
-      </c>
-      <c r="K31" s="20">
-        <f>K29*K30</f>
-        <v/>
-      </c>
-      <c r="L31" s="20">
-        <f>L29*L30</f>
-        <v/>
-      </c>
-      <c r="M31" s="20">
-        <f>M29*M30</f>
-        <v/>
-      </c>
-      <c r="N31" s="20">
-        <f>N29*N30</f>
-        <v/>
-      </c>
-      <c r="O31" s="20">
-        <f>O29*O30</f>
-        <v/>
-      </c>
-      <c r="P31" s="20">
-        <f>P29*P30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>Sum PV Abnormal Earnings</t>
-        </is>
-      </c>
-      <c r="G35" s="20">
-        <f>SUM(G31:P31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>Terminal Value</t>
-        </is>
-      </c>
-      <c r="P36" s="20">
-        <f>P29*(1+$B$9)/($B$5-$B$9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>PV Terminal Value</t>
-        </is>
-      </c>
-      <c r="G37" s="20">
-        <f>P36*P30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Intrinsic Value</t>
-        </is>
-      </c>
-      <c r="G38" s="20">
-        <f>G26+G35+G37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>Diluted Shares</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Intrinsic Value per Share</t>
-        </is>
-      </c>
-      <c r="G40" s="30">
-        <f>G38/G39</f>
-        <v/>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Deferred from historical-only v1</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6037,727 +4651,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Demo Holdings Limited — Base Scenario</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Cost of Equity (Ke)</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="n">
-        <v>0.0975</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n">
-        <v>0.165</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>After-tax CoD</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n">
-        <v>-0.2273251281748943</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>Financial leverage</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n">
-        <v>-0.09433962264150944</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Terminal growth (g)</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>FORECAST BLOCK</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="L20" s="15" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
-      </c>
-      <c r="M20" s="15" t="inlineStr">
-        <is>
-          <t>Y7</t>
-        </is>
-      </c>
-      <c r="N20" s="15" t="inlineStr">
-        <is>
-          <t>Y8</t>
-        </is>
-      </c>
-      <c r="O20" s="15" t="inlineStr">
-        <is>
-          <t>Y9</t>
-        </is>
-      </c>
-      <c r="P20" s="15" t="inlineStr">
-        <is>
-          <t>Y10</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="G21" s="26">
-        <f>'Income Statement'!F7*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="H21" s="19">
-        <f>G21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="I21" s="19">
-        <f>H21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="J21" s="19">
-        <f>I21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="K21" s="19">
-        <f>J21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="L21" s="19">
-        <f>K21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="M21" s="19">
-        <f>L21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="N21" s="19">
-        <f>M21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="O21" s="19">
-        <f>N21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="P21" s="19">
-        <f>O21*(1+0.1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>NOPAT Margin</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>NOWC</t>
-        </is>
-      </c>
-      <c r="G23" s="19">
-        <f>'Condensed Financials'!F31</f>
-        <v/>
-      </c>
-      <c r="H23" s="19">
-        <f>H21*0.05</f>
-        <v/>
-      </c>
-      <c r="I23" s="19">
-        <f>I21*0.05</f>
-        <v/>
-      </c>
-      <c r="J23" s="19">
-        <f>J21*0.05</f>
-        <v/>
-      </c>
-      <c r="K23" s="19">
-        <f>K21*0.05</f>
-        <v/>
-      </c>
-      <c r="L23" s="19">
-        <f>L21*0.05</f>
-        <v/>
-      </c>
-      <c r="M23" s="19">
-        <f>M21*0.05</f>
-        <v/>
-      </c>
-      <c r="N23" s="19">
-        <f>N21*0.05</f>
-        <v/>
-      </c>
-      <c r="O23" s="19">
-        <f>O21*0.05</f>
-        <v/>
-      </c>
-      <c r="P23" s="19">
-        <f>P21*0.05</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>NOLA</t>
-        </is>
-      </c>
-      <c r="G24" s="19">
-        <f>'Condensed Financials'!F35-'Condensed Financials'!F31</f>
-        <v/>
-      </c>
-      <c r="H24" s="19">
-        <f>H21*0.5</f>
-        <v/>
-      </c>
-      <c r="I24" s="19">
-        <f>I21*0.5</f>
-        <v/>
-      </c>
-      <c r="J24" s="19">
-        <f>J21*0.5</f>
-        <v/>
-      </c>
-      <c r="K24" s="19">
-        <f>K21*0.5</f>
-        <v/>
-      </c>
-      <c r="L24" s="19">
-        <f>L21*0.5</f>
-        <v/>
-      </c>
-      <c r="M24" s="19">
-        <f>M21*0.5</f>
-        <v/>
-      </c>
-      <c r="N24" s="19">
-        <f>N21*0.5</f>
-        <v/>
-      </c>
-      <c r="O24" s="19">
-        <f>O21*0.5</f>
-        <v/>
-      </c>
-      <c r="P24" s="19">
-        <f>P21*0.5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>Net Debt</t>
-        </is>
-      </c>
-      <c r="G25" s="20">
-        <f>'Condensed Financials'!F38</f>
-        <v/>
-      </c>
-      <c r="H25" s="20">
-        <f>($B$8)*(H23+H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="20">
-        <f>($B$8)*(I23+I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="20">
-        <f>($B$8)*(J23+J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="20">
-        <f>($B$8)*(K23+K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="20">
-        <f>($B$8)*(L23+L24)</f>
-        <v/>
-      </c>
-      <c r="M25" s="20">
-        <f>($B$8)*(M23+M24)</f>
-        <v/>
-      </c>
-      <c r="N25" s="20">
-        <f>($B$8)*(N23+N24)</f>
-        <v/>
-      </c>
-      <c r="O25" s="20">
-        <f>($B$8)*(O23+O24)</f>
-        <v/>
-      </c>
-      <c r="P25" s="20">
-        <f>($B$8)*(P23+P24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>Book Equity</t>
-        </is>
-      </c>
-      <c r="G26" s="20">
-        <f>G23+G24-G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="20">
-        <f>H23+H24-H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="20">
-        <f>I23+I24-I25</f>
-        <v/>
-      </c>
-      <c r="J26" s="20">
-        <f>J23+J24-J25</f>
-        <v/>
-      </c>
-      <c r="K26" s="20">
-        <f>K23+K24-K25</f>
-        <v/>
-      </c>
-      <c r="L26" s="20">
-        <f>L23+L24-L25</f>
-        <v/>
-      </c>
-      <c r="M26" s="20">
-        <f>M23+M24-M25</f>
-        <v/>
-      </c>
-      <c r="N26" s="20">
-        <f>N23+N24-N25</f>
-        <v/>
-      </c>
-      <c r="O26" s="20">
-        <f>O23+O24-O25</f>
-        <v/>
-      </c>
-      <c r="P26" s="20">
-        <f>P23+P24-P25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>NOPAT</t>
-        </is>
-      </c>
-      <c r="G27" s="26">
-        <f>G21*G22</f>
-        <v/>
-      </c>
-      <c r="H27" s="19">
-        <f>H21*H22</f>
-        <v/>
-      </c>
-      <c r="I27" s="19">
-        <f>I21*I22</f>
-        <v/>
-      </c>
-      <c r="J27" s="19">
-        <f>J21*J22</f>
-        <v/>
-      </c>
-      <c r="K27" s="19">
-        <f>K21*K22</f>
-        <v/>
-      </c>
-      <c r="L27" s="19">
-        <f>L21*L22</f>
-        <v/>
-      </c>
-      <c r="M27" s="19">
-        <f>M21*M22</f>
-        <v/>
-      </c>
-      <c r="N27" s="19">
-        <f>N21*N22</f>
-        <v/>
-      </c>
-      <c r="O27" s="19">
-        <f>O21*O22</f>
-        <v/>
-      </c>
-      <c r="P27" s="19">
-        <f>P21*P22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="G28" s="20">
-        <f>G27-G25*$B$7</f>
-        <v/>
-      </c>
-      <c r="H28" s="20">
-        <f>H27-H25*$B$7</f>
-        <v/>
-      </c>
-      <c r="I28" s="20">
-        <f>I27-I25*$B$7</f>
-        <v/>
-      </c>
-      <c r="J28" s="20">
-        <f>J27-J25*$B$7</f>
-        <v/>
-      </c>
-      <c r="K28" s="20">
-        <f>K27-K25*$B$7</f>
-        <v/>
-      </c>
-      <c r="L28" s="20">
-        <f>L27-L25*$B$7</f>
-        <v/>
-      </c>
-      <c r="M28" s="20">
-        <f>M27-M25*$B$7</f>
-        <v/>
-      </c>
-      <c r="N28" s="20">
-        <f>N27-N25*$B$7</f>
-        <v/>
-      </c>
-      <c r="O28" s="20">
-        <f>O27-O25*$B$7</f>
-        <v/>
-      </c>
-      <c r="P28" s="20">
-        <f>P27-P25*$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Abnormal Earnings</t>
-        </is>
-      </c>
-      <c r="G29" s="23">
-        <f>G28-$B$5*G26</f>
-        <v/>
-      </c>
-      <c r="H29" s="20">
-        <f>H28-$B$5*H26</f>
-        <v/>
-      </c>
-      <c r="I29" s="20">
-        <f>I28-$B$5*I26</f>
-        <v/>
-      </c>
-      <c r="J29" s="20">
-        <f>J28-$B$5*J26</f>
-        <v/>
-      </c>
-      <c r="K29" s="20">
-        <f>K28-$B$5*K26</f>
-        <v/>
-      </c>
-      <c r="L29" s="20">
-        <f>L28-$B$5*L26</f>
-        <v/>
-      </c>
-      <c r="M29" s="20">
-        <f>M28-$B$5*M26</f>
-        <v/>
-      </c>
-      <c r="N29" s="20">
-        <f>N28-$B$5*N26</f>
-        <v/>
-      </c>
-      <c r="O29" s="20">
-        <f>O28-$B$5*O26</f>
-        <v/>
-      </c>
-      <c r="P29" s="20">
-        <f>P28-$B$5*P26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Discount Factor</t>
-        </is>
-      </c>
-      <c r="G30" s="30">
-        <f>1/(1+$B$5)^1</f>
-        <v/>
-      </c>
-      <c r="H30" s="30">
-        <f>1/(1+$B$5)^2</f>
-        <v/>
-      </c>
-      <c r="I30" s="30">
-        <f>1/(1+$B$5)^3</f>
-        <v/>
-      </c>
-      <c r="J30" s="30">
-        <f>1/(1+$B$5)^4</f>
-        <v/>
-      </c>
-      <c r="K30" s="30">
-        <f>1/(1+$B$5)^5</f>
-        <v/>
-      </c>
-      <c r="L30" s="30">
-        <f>1/(1+$B$5)^6</f>
-        <v/>
-      </c>
-      <c r="M30" s="30">
-        <f>1/(1+$B$5)^7</f>
-        <v/>
-      </c>
-      <c r="N30" s="30">
-        <f>1/(1+$B$5)^8</f>
-        <v/>
-      </c>
-      <c r="O30" s="30">
-        <f>1/(1+$B$5)^9</f>
-        <v/>
-      </c>
-      <c r="P30" s="30">
-        <f>1/(1+$B$5)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>PV Abnormal Earnings</t>
-        </is>
-      </c>
-      <c r="G31" s="20">
-        <f>G29*G30</f>
-        <v/>
-      </c>
-      <c r="H31" s="20">
-        <f>H29*H30</f>
-        <v/>
-      </c>
-      <c r="I31" s="20">
-        <f>I29*I30</f>
-        <v/>
-      </c>
-      <c r="J31" s="20">
-        <f>J29*J30</f>
-        <v/>
-      </c>
-      <c r="K31" s="20">
-        <f>K29*K30</f>
-        <v/>
-      </c>
-      <c r="L31" s="20">
-        <f>L29*L30</f>
-        <v/>
-      </c>
-      <c r="M31" s="20">
-        <f>M29*M30</f>
-        <v/>
-      </c>
-      <c r="N31" s="20">
-        <f>N29*N30</f>
-        <v/>
-      </c>
-      <c r="O31" s="20">
-        <f>O29*O30</f>
-        <v/>
-      </c>
-      <c r="P31" s="20">
-        <f>P29*P30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>Sum PV Abnormal Earnings</t>
-        </is>
-      </c>
-      <c r="G35" s="20">
-        <f>SUM(G31:P31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>Terminal Value</t>
-        </is>
-      </c>
-      <c r="P36" s="20">
-        <f>P29*(1+$B$9)/($B$5-$B$9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>PV Terminal Value</t>
-        </is>
-      </c>
-      <c r="G37" s="23">
-        <f>P36*P30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Intrinsic Value</t>
-        </is>
-      </c>
-      <c r="G38" s="20">
-        <f>G26+G35+G37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>Diluted Shares</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Intrinsic Value per Share</t>
-        </is>
-      </c>
-      <c r="G40" s="31">
-        <f>G38/G39</f>
-        <v/>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Deferred from historical-only v1</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -6767,722 +4672,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Demo Holdings Limited — Bull Scenario</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Cost of Equity (Ke)</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="n">
-        <v>0.0925</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n">
-        <v>0.165</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>After-tax CoD</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n">
-        <v>-0.2273251281748943</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>Financial leverage</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n">
-        <v>-0.09433962264150944</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Terminal growth (g)</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>FORECAST BLOCK</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="J20" s="15" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="L20" s="15" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
-      </c>
-      <c r="M20" s="15" t="inlineStr">
-        <is>
-          <t>Y7</t>
-        </is>
-      </c>
-      <c r="N20" s="15" t="inlineStr">
-        <is>
-          <t>Y8</t>
-        </is>
-      </c>
-      <c r="O20" s="15" t="inlineStr">
-        <is>
-          <t>Y9</t>
-        </is>
-      </c>
-      <c r="P20" s="15" t="inlineStr">
-        <is>
-          <t>Y10</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="G21" s="19">
-        <f>'Income Statement'!F7*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="H21" s="19">
-        <f>G21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="I21" s="19">
-        <f>H21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="J21" s="19">
-        <f>I21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="K21" s="19">
-        <f>J21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="L21" s="19">
-        <f>K21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="M21" s="19">
-        <f>L21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="N21" s="19">
-        <f>M21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="O21" s="19">
-        <f>N21*(1+0.1)</f>
-        <v/>
-      </c>
-      <c r="P21" s="19">
-        <f>O21*(1+0.1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>NOPAT Margin</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="N22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P22" s="21" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>NOWC</t>
-        </is>
-      </c>
-      <c r="G23" s="19">
-        <f>'Condensed Financials'!F31</f>
-        <v/>
-      </c>
-      <c r="H23" s="19">
-        <f>H21*0.05</f>
-        <v/>
-      </c>
-      <c r="I23" s="19">
-        <f>I21*0.05</f>
-        <v/>
-      </c>
-      <c r="J23" s="19">
-        <f>J21*0.05</f>
-        <v/>
-      </c>
-      <c r="K23" s="19">
-        <f>K21*0.05</f>
-        <v/>
-      </c>
-      <c r="L23" s="19">
-        <f>L21*0.05</f>
-        <v/>
-      </c>
-      <c r="M23" s="19">
-        <f>M21*0.05</f>
-        <v/>
-      </c>
-      <c r="N23" s="19">
-        <f>N21*0.05</f>
-        <v/>
-      </c>
-      <c r="O23" s="19">
-        <f>O21*0.05</f>
-        <v/>
-      </c>
-      <c r="P23" s="19">
-        <f>P21*0.05</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>NOLA</t>
-        </is>
-      </c>
-      <c r="G24" s="19">
-        <f>'Condensed Financials'!F35-'Condensed Financials'!F31</f>
-        <v/>
-      </c>
-      <c r="H24" s="19">
-        <f>H21*0.5</f>
-        <v/>
-      </c>
-      <c r="I24" s="19">
-        <f>I21*0.5</f>
-        <v/>
-      </c>
-      <c r="J24" s="19">
-        <f>J21*0.5</f>
-        <v/>
-      </c>
-      <c r="K24" s="19">
-        <f>K21*0.5</f>
-        <v/>
-      </c>
-      <c r="L24" s="19">
-        <f>L21*0.5</f>
-        <v/>
-      </c>
-      <c r="M24" s="19">
-        <f>M21*0.5</f>
-        <v/>
-      </c>
-      <c r="N24" s="19">
-        <f>N21*0.5</f>
-        <v/>
-      </c>
-      <c r="O24" s="19">
-        <f>O21*0.5</f>
-        <v/>
-      </c>
-      <c r="P24" s="19">
-        <f>P21*0.5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>Net Debt</t>
-        </is>
-      </c>
-      <c r="G25" s="20">
-        <f>'Condensed Financials'!F38</f>
-        <v/>
-      </c>
-      <c r="H25" s="20">
-        <f>($B$8)*(H23+H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="20">
-        <f>($B$8)*(I23+I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="20">
-        <f>($B$8)*(J23+J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="20">
-        <f>($B$8)*(K23+K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="20">
-        <f>($B$8)*(L23+L24)</f>
-        <v/>
-      </c>
-      <c r="M25" s="20">
-        <f>($B$8)*(M23+M24)</f>
-        <v/>
-      </c>
-      <c r="N25" s="20">
-        <f>($B$8)*(N23+N24)</f>
-        <v/>
-      </c>
-      <c r="O25" s="20">
-        <f>($B$8)*(O23+O24)</f>
-        <v/>
-      </c>
-      <c r="P25" s="20">
-        <f>($B$8)*(P23+P24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>Book Equity</t>
-        </is>
-      </c>
-      <c r="G26" s="20">
-        <f>G23+G24-G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="20">
-        <f>H23+H24-H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="20">
-        <f>I23+I24-I25</f>
-        <v/>
-      </c>
-      <c r="J26" s="20">
-        <f>J23+J24-J25</f>
-        <v/>
-      </c>
-      <c r="K26" s="20">
-        <f>K23+K24-K25</f>
-        <v/>
-      </c>
-      <c r="L26" s="20">
-        <f>L23+L24-L25</f>
-        <v/>
-      </c>
-      <c r="M26" s="20">
-        <f>M23+M24-M25</f>
-        <v/>
-      </c>
-      <c r="N26" s="20">
-        <f>N23+N24-N25</f>
-        <v/>
-      </c>
-      <c r="O26" s="20">
-        <f>O23+O24-O25</f>
-        <v/>
-      </c>
-      <c r="P26" s="20">
-        <f>P23+P24-P25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>NOPAT</t>
-        </is>
-      </c>
-      <c r="G27" s="19">
-        <f>G21*G22</f>
-        <v/>
-      </c>
-      <c r="H27" s="19">
-        <f>H21*H22</f>
-        <v/>
-      </c>
-      <c r="I27" s="19">
-        <f>I21*I22</f>
-        <v/>
-      </c>
-      <c r="J27" s="19">
-        <f>J21*J22</f>
-        <v/>
-      </c>
-      <c r="K27" s="19">
-        <f>K21*K22</f>
-        <v/>
-      </c>
-      <c r="L27" s="19">
-        <f>L21*L22</f>
-        <v/>
-      </c>
-      <c r="M27" s="19">
-        <f>M21*M22</f>
-        <v/>
-      </c>
-      <c r="N27" s="19">
-        <f>N21*N22</f>
-        <v/>
-      </c>
-      <c r="O27" s="19">
-        <f>O21*O22</f>
-        <v/>
-      </c>
-      <c r="P27" s="19">
-        <f>P21*P22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="G28" s="20">
-        <f>G27-G25*$B$7</f>
-        <v/>
-      </c>
-      <c r="H28" s="20">
-        <f>H27-H25*$B$7</f>
-        <v/>
-      </c>
-      <c r="I28" s="20">
-        <f>I27-I25*$B$7</f>
-        <v/>
-      </c>
-      <c r="J28" s="20">
-        <f>J27-J25*$B$7</f>
-        <v/>
-      </c>
-      <c r="K28" s="20">
-        <f>K27-K25*$B$7</f>
-        <v/>
-      </c>
-      <c r="L28" s="20">
-        <f>L27-L25*$B$7</f>
-        <v/>
-      </c>
-      <c r="M28" s="20">
-        <f>M27-M25*$B$7</f>
-        <v/>
-      </c>
-      <c r="N28" s="20">
-        <f>N27-N25*$B$7</f>
-        <v/>
-      </c>
-      <c r="O28" s="20">
-        <f>O27-O25*$B$7</f>
-        <v/>
-      </c>
-      <c r="P28" s="20">
-        <f>P27-P25*$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Abnormal Earnings</t>
-        </is>
-      </c>
-      <c r="G29" s="20">
-        <f>G28-$B$5*G26</f>
-        <v/>
-      </c>
-      <c r="H29" s="20">
-        <f>H28-$B$5*H26</f>
-        <v/>
-      </c>
-      <c r="I29" s="20">
-        <f>I28-$B$5*I26</f>
-        <v/>
-      </c>
-      <c r="J29" s="20">
-        <f>J28-$B$5*J26</f>
-        <v/>
-      </c>
-      <c r="K29" s="20">
-        <f>K28-$B$5*K26</f>
-        <v/>
-      </c>
-      <c r="L29" s="20">
-        <f>L28-$B$5*L26</f>
-        <v/>
-      </c>
-      <c r="M29" s="20">
-        <f>M28-$B$5*M26</f>
-        <v/>
-      </c>
-      <c r="N29" s="20">
-        <f>N28-$B$5*N26</f>
-        <v/>
-      </c>
-      <c r="O29" s="20">
-        <f>O28-$B$5*O26</f>
-        <v/>
-      </c>
-      <c r="P29" s="20">
-        <f>P28-$B$5*P26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Discount Factor</t>
-        </is>
-      </c>
-      <c r="G30" s="30">
-        <f>1/(1+$B$5)^1</f>
-        <v/>
-      </c>
-      <c r="H30" s="30">
-        <f>1/(1+$B$5)^2</f>
-        <v/>
-      </c>
-      <c r="I30" s="30">
-        <f>1/(1+$B$5)^3</f>
-        <v/>
-      </c>
-      <c r="J30" s="30">
-        <f>1/(1+$B$5)^4</f>
-        <v/>
-      </c>
-      <c r="K30" s="30">
-        <f>1/(1+$B$5)^5</f>
-        <v/>
-      </c>
-      <c r="L30" s="30">
-        <f>1/(1+$B$5)^6</f>
-        <v/>
-      </c>
-      <c r="M30" s="30">
-        <f>1/(1+$B$5)^7</f>
-        <v/>
-      </c>
-      <c r="N30" s="30">
-        <f>1/(1+$B$5)^8</f>
-        <v/>
-      </c>
-      <c r="O30" s="30">
-        <f>1/(1+$B$5)^9</f>
-        <v/>
-      </c>
-      <c r="P30" s="30">
-        <f>1/(1+$B$5)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>PV Abnormal Earnings</t>
-        </is>
-      </c>
-      <c r="G31" s="20">
-        <f>G29*G30</f>
-        <v/>
-      </c>
-      <c r="H31" s="20">
-        <f>H29*H30</f>
-        <v/>
-      </c>
-      <c r="I31" s="20">
-        <f>I29*I30</f>
-        <v/>
-      </c>
-      <c r="J31" s="20">
-        <f>J29*J30</f>
-        <v/>
-      </c>
-      <c r="K31" s="20">
-        <f>K29*K30</f>
-        <v/>
-      </c>
-      <c r="L31" s="20">
-        <f>L29*L30</f>
-        <v/>
-      </c>
-      <c r="M31" s="20">
-        <f>M29*M30</f>
-        <v/>
-      </c>
-      <c r="N31" s="20">
-        <f>N29*N30</f>
-        <v/>
-      </c>
-      <c r="O31" s="20">
-        <f>O29*O30</f>
-        <v/>
-      </c>
-      <c r="P31" s="20">
-        <f>P29*P30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>Sum PV Abnormal Earnings</t>
-        </is>
-      </c>
-      <c r="G35" s="20">
-        <f>SUM(G31:P31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>Terminal Value</t>
-        </is>
-      </c>
-      <c r="P36" s="20">
-        <f>P29*(1+$B$9)/($B$5-$B$9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>PV Terminal Value</t>
-        </is>
-      </c>
-      <c r="G37" s="20">
-        <f>P36*P30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Intrinsic Value</t>
-        </is>
-      </c>
-      <c r="G38" s="20">
-        <f>G26+G35+G37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>Diluted Shares</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Intrinsic Value per Share</t>
-        </is>
-      </c>
-      <c r="G40" s="30">
-        <f>G38/G39</f>
-        <v/>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Deferred from historical-only v1</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/example/DEMO_HK_Answer_Key.xlsx
+++ b/example/DEMO_HK_Answer_Key.xlsx
@@ -13,11 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condensed Financials" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALT DuPont" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Bear" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Base" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Bull" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario_Summary" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ComponentMap" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accounting Judgment" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Bear" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Base" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Bull" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario_Summary" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_ComponentMap" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -75,12 +76,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +119,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,13 +128,13 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -215,179 +217,154 @@
     <author>BAV Trainer</author>
   </authors>
   <commentList>
-    <comment ref="B18" authorId="0" shapeId="0">
+    <comment ref="B19" authorId="0" shapeId="0">
       <text>
         <t>Link Revenue from the Income Statement into Condensed Financials.</t>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
+    <comment ref="C19" authorId="0" shapeId="0">
       <text>
         <t>Link Revenue from the Income Statement into Condensed Financials.</t>
       </text>
     </comment>
-    <comment ref="D18" authorId="0" shapeId="0">
+    <comment ref="D19" authorId="0" shapeId="0">
       <text>
         <t>Link Revenue from the Income Statement into Condensed Financials.</t>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0">
+    <comment ref="E19" authorId="0" shapeId="0">
       <text>
         <t>Link Revenue from the Income Statement into Condensed Financials.</t>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0">
+    <comment ref="F19" authorId="0" shapeId="0">
       <text>
         <t>Link Revenue from the Income Statement into Condensed Financials.</t>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0">
+    <comment ref="B20" authorId="0" shapeId="0">
       <text>
         <t>Link Net Income from the Income Statement into Condensed Financials.</t>
       </text>
     </comment>
-    <comment ref="C19" authorId="0" shapeId="0">
+    <comment ref="C20" authorId="0" shapeId="0">
       <text>
         <t>Link Net Income from the Income Statement into Condensed Financials.</t>
       </text>
     </comment>
-    <comment ref="D19" authorId="0" shapeId="0">
+    <comment ref="D20" authorId="0" shapeId="0">
       <text>
         <t>Link Net Income from the Income Statement into Condensed Financials.</t>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0">
+    <comment ref="E20" authorId="0" shapeId="0">
       <text>
         <t>Link Net Income from the Income Statement into Condensed Financials.</t>
       </text>
     </comment>
-    <comment ref="F19" authorId="0" shapeId="0">
+    <comment ref="F20" authorId="0" shapeId="0">
       <text>
         <t>Link Net Income from the Income Statement into Condensed Financials.</t>
       </text>
     </comment>
-    <comment ref="B24" authorId="0" shapeId="0">
+    <comment ref="B25" authorId="0" shapeId="0">
       <text>
         <t>Relate tax expense to pretax income using the model's sign convention.</t>
       </text>
     </comment>
-    <comment ref="C24" authorId="0" shapeId="0">
+    <comment ref="C25" authorId="0" shapeId="0">
       <text>
         <t>Relate tax expense to pretax income using the model's sign convention.</t>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0">
+    <comment ref="D25" authorId="0" shapeId="0">
       <text>
         <t>Relate tax expense to pretax income using the model's sign convention.</t>
       </text>
     </comment>
-    <comment ref="E24" authorId="0" shapeId="0">
+    <comment ref="E25" authorId="0" shapeId="0">
       <text>
         <t>Relate tax expense to pretax income using the model's sign convention.</t>
       </text>
     </comment>
-    <comment ref="F24" authorId="0" shapeId="0">
+    <comment ref="F25" authorId="0" shapeId="0">
       <text>
         <t>Relate tax expense to pretax income using the model's sign convention.</t>
       </text>
     </comment>
-    <comment ref="B25" authorId="0" shapeId="0">
+    <comment ref="B26" authorId="0" shapeId="0">
       <text>
         <t>Combine interest expense and interest income into the financing result.</t>
       </text>
     </comment>
-    <comment ref="C25" authorId="0" shapeId="0">
+    <comment ref="C26" authorId="0" shapeId="0">
       <text>
         <t>Combine interest expense and interest income into the financing result.</t>
       </text>
     </comment>
-    <comment ref="D25" authorId="0" shapeId="0">
+    <comment ref="D26" authorId="0" shapeId="0">
       <text>
         <t>Combine interest expense and interest income into the financing result.</t>
       </text>
     </comment>
-    <comment ref="E25" authorId="0" shapeId="0">
+    <comment ref="E26" authorId="0" shapeId="0">
       <text>
         <t>Combine interest expense and interest income into the financing result.</t>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F26" authorId="0" shapeId="0">
       <text>
         <t>Combine interest expense and interest income into the financing result.</t>
       </text>
     </comment>
-    <comment ref="B26" authorId="0" shapeId="0">
+    <comment ref="B27" authorId="0" shapeId="0">
       <text>
         <t>Apply the effective tax rate once to net interest.</t>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
+    <comment ref="C27" authorId="0" shapeId="0">
       <text>
         <t>Apply the effective tax rate once to net interest.</t>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0">
+    <comment ref="D27" authorId="0" shapeId="0">
       <text>
         <t>Apply the effective tax rate once to net interest.</t>
       </text>
     </comment>
-    <comment ref="E26" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0" shapeId="0">
       <text>
         <t>Apply the effective tax rate once to net interest.</t>
       </text>
     </comment>
-    <comment ref="F26" authorId="0" shapeId="0">
+    <comment ref="F27" authorId="0" shapeId="0">
       <text>
         <t>Apply the effective tax rate once to net interest.</t>
       </text>
     </comment>
-    <comment ref="B27" authorId="0" shapeId="0">
+    <comment ref="B28" authorId="0" shapeId="0">
       <text>
         <t>Reformulate net income to operating profit after tax.</t>
       </text>
     </comment>
-    <comment ref="C27" authorId="0" shapeId="0">
+    <comment ref="C28" authorId="0" shapeId="0">
       <text>
         <t>Reformulate net income to operating profit after tax.</t>
       </text>
     </comment>
-    <comment ref="D27" authorId="0" shapeId="0">
+    <comment ref="D28" authorId="0" shapeId="0">
       <text>
         <t>Reformulate net income to operating profit after tax.</t>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E28" authorId="0" shapeId="0">
       <text>
         <t>Reformulate net income to operating profit after tax.</t>
       </text>
     </comment>
-    <comment ref="F27" authorId="0" shapeId="0">
+    <comment ref="F28" authorId="0" shapeId="0">
       <text>
         <t>Reformulate net income to operating profit after tax.</t>
-      </text>
-    </comment>
-    <comment ref="B30" authorId="0" shapeId="0">
-      <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
-      </text>
-    </comment>
-    <comment ref="C30" authorId="0" shapeId="0">
-      <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
-      </text>
-    </comment>
-    <comment ref="D30" authorId="0" shapeId="0">
-      <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
-      </text>
-    </comment>
-    <comment ref="E30" authorId="0" shapeId="0">
-      <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
-      </text>
-    </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
-      <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
@@ -417,52 +394,52 @@
     </comment>
     <comment ref="B32" authorId="0" shapeId="0">
       <text>
-        <t>Sum operating WC assets minus operating WC liabilities.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="C32" authorId="0" shapeId="0">
       <text>
-        <t>Sum operating WC assets minus operating WC liabilities.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="D32" authorId="0" shapeId="0">
       <text>
-        <t>Sum operating WC assets minus operating WC liabilities.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="E32" authorId="0" shapeId="0">
       <text>
-        <t>Sum operating WC assets minus operating WC liabilities.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="F32" authorId="0" shapeId="0">
       <text>
-        <t>Sum operating WC assets minus operating WC liabilities.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="B33" authorId="0" shapeId="0">
       <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+        <t>Sum operating WC assets minus operating WC liabilities.</t>
       </text>
     </comment>
     <comment ref="C33" authorId="0" shapeId="0">
       <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+        <t>Sum operating WC assets minus operating WC liabilities.</t>
       </text>
     </comment>
     <comment ref="D33" authorId="0" shapeId="0">
       <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+        <t>Sum operating WC assets minus operating WC liabilities.</t>
       </text>
     </comment>
     <comment ref="E33" authorId="0" shapeId="0">
       <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+        <t>Sum operating WC assets minus operating WC liabilities.</t>
       </text>
     </comment>
     <comment ref="F33" authorId="0" shapeId="0">
       <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+        <t>Sum operating WC assets minus operating WC liabilities.</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
@@ -492,77 +469,77 @@
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>Operating long-term assets less operating long-term liabilities.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="C35" authorId="0" shapeId="0">
       <text>
-        <t>Operating long-term assets less operating long-term liabilities.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="D35" authorId="0" shapeId="0">
       <text>
-        <t>Operating long-term assets less operating long-term liabilities.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="E35" authorId="0" shapeId="0">
       <text>
-        <t>Operating long-term assets less operating long-term liabilities.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="F35" authorId="0" shapeId="0">
       <text>
-        <t>Operating long-term assets less operating long-term liabilities.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="B36" authorId="0" shapeId="0">
       <text>
-        <t>NOWC plus net operating long-term assets.</t>
+        <t>Operating long-term assets less operating long-term liabilities.</t>
       </text>
     </comment>
     <comment ref="C36" authorId="0" shapeId="0">
       <text>
-        <t>NOWC plus net operating long-term assets.</t>
+        <t>Operating long-term assets less operating long-term liabilities.</t>
       </text>
     </comment>
     <comment ref="D36" authorId="0" shapeId="0">
       <text>
-        <t>NOWC plus net operating long-term assets.</t>
+        <t>Operating long-term assets less operating long-term liabilities.</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
       <text>
-        <t>NOWC plus net operating long-term assets.</t>
+        <t>Operating long-term assets less operating long-term liabilities.</t>
       </text>
     </comment>
     <comment ref="F36" authorId="0" shapeId="0">
       <text>
-        <t>NOWC plus net operating long-term assets.</t>
+        <t>Operating long-term assets less operating long-term liabilities.</t>
       </text>
     </comment>
     <comment ref="B37" authorId="0" shapeId="0">
       <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+        <t>NOWC plus net operating long-term assets.</t>
       </text>
     </comment>
     <comment ref="C37" authorId="0" shapeId="0">
       <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+        <t>NOWC plus net operating long-term assets.</t>
       </text>
     </comment>
     <comment ref="D37" authorId="0" shapeId="0">
       <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+        <t>NOWC plus net operating long-term assets.</t>
       </text>
     </comment>
     <comment ref="E37" authorId="0" shapeId="0">
       <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+        <t>NOWC plus net operating long-term assets.</t>
       </text>
     </comment>
     <comment ref="F37" authorId="0" shapeId="0">
       <text>
-        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
+        <t>NOWC plus net operating long-term assets.</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
@@ -592,50 +569,75 @@
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>Financial liabilities minus financial assets.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="C39" authorId="0" shapeId="0">
       <text>
-        <t>Financial liabilities minus financial assets.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="D39" authorId="0" shapeId="0">
       <text>
-        <t>Financial liabilities minus financial assets.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="E39" authorId="0" shapeId="0">
       <text>
-        <t>Financial liabilities minus financial assets.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="F39" authorId="0" shapeId="0">
       <text>
-        <t>Financial liabilities minus financial assets.</t>
+        <t>Aggregate the classified balance-sheet detail with the classification column.</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>Use the operating/financing identity linking NOA, Net Debt, and Equity.</t>
+        <t>Financial liabilities minus financial assets.</t>
       </text>
     </comment>
     <comment ref="C40" authorId="0" shapeId="0">
       <text>
-        <t>Use the operating/financing identity linking NOA, Net Debt, and Equity.</t>
+        <t>Financial liabilities minus financial assets.</t>
       </text>
     </comment>
     <comment ref="D40" authorId="0" shapeId="0">
       <text>
-        <t>Use the operating/financing identity linking NOA, Net Debt, and Equity.</t>
+        <t>Financial liabilities minus financial assets.</t>
       </text>
     </comment>
     <comment ref="E40" authorId="0" shapeId="0">
       <text>
+        <t>Financial liabilities minus financial assets.</t>
+      </text>
+    </comment>
+    <comment ref="F40" authorId="0" shapeId="0">
+      <text>
+        <t>Financial liabilities minus financial assets.</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
         <t>Use the operating/financing identity linking NOA, Net Debt, and Equity.</t>
       </text>
     </comment>
-    <comment ref="F40" authorId="0" shapeId="0">
+    <comment ref="C41" authorId="0" shapeId="0">
+      <text>
+        <t>Use the operating/financing identity linking NOA, Net Debt, and Equity.</t>
+      </text>
+    </comment>
+    <comment ref="D41" authorId="0" shapeId="0">
+      <text>
+        <t>Use the operating/financing identity linking NOA, Net Debt, and Equity.</t>
+      </text>
+    </comment>
+    <comment ref="E41" authorId="0" shapeId="0">
+      <text>
+        <t>Use the operating/financing identity linking NOA, Net Debt, and Equity.</t>
+      </text>
+    </comment>
+    <comment ref="F41" authorId="0" shapeId="0">
       <text>
         <t>Use the operating/financing identity linking NOA, Net Debt, and Equity.</t>
       </text>
@@ -1120,796 +1122,796 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>BAV Excel Trainer</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Complete each historical schedule left-to-right in dependency order. Each schedule is one modeling concept repeated across fiscal periods. Run Check to validate every yellow cell in the workbook. Open the matching Answer Key for the formula/input and Note hint.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Period scope</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Tab</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Practice cells</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Depends on</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Revenue historical source link</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>B18:F18</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>B19:F19</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Net Income historical source link</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>B19:F19</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>B20:F20</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Effective tax rate</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>B24:F24</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>B25:F25</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Net interest</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>B25:F25</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>B26:F26</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Net interest after tax</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>B26:F26</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>B27:F27</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>effective_tax_rate_fy, net_interest_fy</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>B27:F27</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>B28:F28</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>net_income_link, net_interest_after_tax_fy</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Operating working capital assets</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>B30:F30</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>B31:F31</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Operating working capital liabilities</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>B31:F31</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>B32:F32</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Net Operating Working Capital (NOWC)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>B32:F32</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>B33:F33</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>owca_agg, owcl_agg</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Operating long-term assets</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>B33:F33</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>B34:F34</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Operating long-term liabilities</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>B34:F34</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>B35:F35</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Net operating long-term assets (NOLA)</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>B35:F35</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>B36:F36</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>olta_agg, oltl_agg</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Net Operating Assets (NOA)</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>B36:F36</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>B37:F37</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>nowc_agg, nola_agg</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Financial assets</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>B37:F37</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>B38:F38</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Financial liabilities</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>B38:F38</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>B39:F39</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>B39:F39</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>B40:F40</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>financial_assets_agg, financial_liabilities_agg</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Reformulated equity</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Condensed Financials</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>B40:F40</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>B41:F41</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>noa_agg, net_debt</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Sales Growth</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>C5:F5</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>revenue_link</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>NOPAT Margin</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>2021–2025 (5 cells)</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>B6:F6</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>nopat_fy, revenue_link</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Return on Net Operating Assets (RNOA)</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>C7:F7</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>nopat_fy, noa_agg</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>C8:F8</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>net_interest_after_tax_fy, net_debt</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Operating Spread (RNOA − After-tax CoD)</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>C9:F9</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>rnoa, after_tax_cod</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Financial leverage (FLEV)</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>C10:F10</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>net_debt, equity_reformulated_fy</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>ROE decomposition</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>C11:F11</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>rnoa, spread, flev</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Actual ROE</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>2022–2025 (4 cells)</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>C12:F12</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>net_income_link, equity_reformulated_fy</t>
         </is>
@@ -1930,7 +1932,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Deferred from historical-only v1</t>
         </is>
@@ -1947,6 +1949,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Deferred from historical-only v1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2083,7 +2106,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>B18</t>
+          <t>B19</t>
         </is>
       </c>
       <c r="I2">
@@ -2159,7 +2182,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="I3">
@@ -2235,7 +2258,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="I4">
@@ -2311,7 +2334,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="I5">
@@ -2387,7 +2410,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>F18</t>
+          <t>F19</t>
         </is>
       </c>
       <c r="I6">
@@ -2463,7 +2486,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>B19</t>
+          <t>B20</t>
         </is>
       </c>
       <c r="I7">
@@ -2539,7 +2562,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C20</t>
         </is>
       </c>
       <c r="I8">
@@ -2615,7 +2638,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="I9">
@@ -2691,7 +2714,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="I10">
@@ -2767,7 +2790,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>F19</t>
+          <t>F20</t>
         </is>
       </c>
       <c r="I11">
@@ -2843,11 +2866,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>B24</t>
+          <t>B25</t>
         </is>
       </c>
       <c r="I12">
-        <f>IF(B20=0,0,-B21/B20)</f>
+        <f>IF(B21=0,0,-B22/B21)</f>
         <v/>
       </c>
       <c r="J12" t="n">
@@ -2919,11 +2942,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="I13">
-        <f>IF(C20=0,0,-C21/C20)</f>
+        <f>IF(C21=0,0,-C22/C21)</f>
         <v/>
       </c>
       <c r="J13" t="n">
@@ -2995,11 +3018,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="I14">
-        <f>IF(D20=0,0,-D21/D20)</f>
+        <f>IF(D21=0,0,-D22/D21)</f>
         <v/>
       </c>
       <c r="J14" t="n">
@@ -3071,11 +3094,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E25</t>
         </is>
       </c>
       <c r="I15">
-        <f>IF(E20=0,0,-E21/E20)</f>
+        <f>IF(E21=0,0,-E22/E21)</f>
         <v/>
       </c>
       <c r="J15" t="n">
@@ -3147,11 +3170,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>F24</t>
+          <t>F25</t>
         </is>
       </c>
       <c r="I16">
-        <f>IF(F20=0,0,-F21/F20)</f>
+        <f>IF(F21=0,0,-F22/F21)</f>
         <v/>
       </c>
       <c r="J16" t="n">
@@ -3223,11 +3246,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>B25</t>
+          <t>B26</t>
         </is>
       </c>
       <c r="I17">
-        <f>-(B22+B23)</f>
+        <f>-(B23+B24)</f>
         <v/>
       </c>
       <c r="J17" t="n">
@@ -3299,11 +3322,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="I18">
-        <f>-(C22+C23)</f>
+        <f>-(C23+C24)</f>
         <v/>
       </c>
       <c r="J18" t="n">
@@ -3375,11 +3398,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>D26</t>
         </is>
       </c>
       <c r="I19">
-        <f>-(D22+D23)</f>
+        <f>-(D23+D24)</f>
         <v/>
       </c>
       <c r="J19" t="n">
@@ -3451,11 +3474,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>E25</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="I20">
-        <f>-(E22+E23)</f>
+        <f>-(E23+E24)</f>
         <v/>
       </c>
       <c r="J20" t="n">
@@ -3527,11 +3550,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>F25</t>
+          <t>F26</t>
         </is>
       </c>
       <c r="I21">
-        <f>-(F22+F23)</f>
+        <f>-(F23+F24)</f>
         <v/>
       </c>
       <c r="J21" t="n">
@@ -3603,11 +3626,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>B26</t>
+          <t>B27</t>
         </is>
       </c>
       <c r="I22">
-        <f>B25*(1-B24)</f>
+        <f>B26*(1-B25)</f>
         <v/>
       </c>
       <c r="J22" t="n">
@@ -3684,11 +3707,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="I23">
-        <f>C25*(1-C24)</f>
+        <f>C26*(1-C25)</f>
         <v/>
       </c>
       <c r="J23" t="n">
@@ -3765,11 +3788,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="I24">
-        <f>D25*(1-D24)</f>
+        <f>D26*(1-D25)</f>
         <v/>
       </c>
       <c r="J24" t="n">
@@ -3846,11 +3869,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E27</t>
         </is>
       </c>
       <c r="I25">
-        <f>E25*(1-E24)</f>
+        <f>E26*(1-E25)</f>
         <v/>
       </c>
       <c r="J25" t="n">
@@ -3927,11 +3950,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>F26</t>
+          <t>F27</t>
         </is>
       </c>
       <c r="I26">
-        <f>F25*(1-F24)</f>
+        <f>F26*(1-F25)</f>
         <v/>
       </c>
       <c r="J26" t="n">
@@ -4008,11 +4031,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>B27</t>
+          <t>B28</t>
         </is>
       </c>
       <c r="I27">
-        <f>B19+B26</f>
+        <f>B20+B27</f>
         <v/>
       </c>
       <c r="J27" t="n">
@@ -4089,11 +4112,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="I28">
-        <f>C19+C26</f>
+        <f>C20+C27</f>
         <v/>
       </c>
       <c r="J28" t="n">
@@ -4170,11 +4193,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="I29">
-        <f>D19+D26</f>
+        <f>D20+D27</f>
         <v/>
       </c>
       <c r="J29" t="n">
@@ -4251,11 +4274,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E28</t>
         </is>
       </c>
       <c r="I30">
-        <f>E19+E26</f>
+        <f>E20+E27</f>
         <v/>
       </c>
       <c r="J30" t="n">
@@ -4332,11 +4355,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>F27</t>
+          <t>F28</t>
         </is>
       </c>
       <c r="I31">
-        <f>F19+F26</f>
+        <f>F20+F27</f>
         <v/>
       </c>
       <c r="J31" t="n">
@@ -4413,11 +4436,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>B30</t>
+          <t>B31</t>
         </is>
       </c>
       <c r="I32">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",C$6:C$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",C$6:C$16)</f>
         <v/>
       </c>
       <c r="J32" t="n">
@@ -4489,11 +4512,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="I33">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",D$6:D$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",D$6:D$16)</f>
         <v/>
       </c>
       <c r="J33" t="n">
@@ -4565,11 +4588,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="I34">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",E$6:E$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",E$6:E$16)</f>
         <v/>
       </c>
       <c r="J34" t="n">
@@ -4641,11 +4664,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="I35">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",F$6:F$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",F$6:F$16)</f>
         <v/>
       </c>
       <c r="J35" t="n">
@@ -4717,11 +4740,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>F30</t>
+          <t>F31</t>
         </is>
       </c>
       <c r="I36">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",G$6:G$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",G$6:G$16)</f>
         <v/>
       </c>
       <c r="J36" t="n">
@@ -4793,11 +4816,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>B31</t>
+          <t>B32</t>
         </is>
       </c>
       <c r="I37">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",C$6:C$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",C$6:C$16)</f>
         <v/>
       </c>
       <c r="J37" t="n">
@@ -4869,11 +4892,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C31</t>
+          <t>C32</t>
         </is>
       </c>
       <c r="I38">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",D$6:D$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",D$6:D$16)</f>
         <v/>
       </c>
       <c r="J38" t="n">
@@ -4945,11 +4968,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="I39">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",E$6:E$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",E$6:E$16)</f>
         <v/>
       </c>
       <c r="J39" t="n">
@@ -5021,11 +5044,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="I40">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",F$6:F$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",F$6:F$16)</f>
         <v/>
       </c>
       <c r="J40" t="n">
@@ -5097,11 +5120,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>F31</t>
+          <t>F32</t>
         </is>
       </c>
       <c r="I41">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",G$6:G$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",G$6:G$16)</f>
         <v/>
       </c>
       <c r="J41" t="n">
@@ -5173,11 +5196,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>B32</t>
+          <t>B33</t>
         </is>
       </c>
       <c r="I42">
-        <f>B30-B31</f>
+        <f>B31-B32</f>
         <v/>
       </c>
       <c r="J42" t="n">
@@ -5254,11 +5277,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="I43">
-        <f>C30-C31</f>
+        <f>C31-C32</f>
         <v/>
       </c>
       <c r="J43" t="n">
@@ -5335,11 +5358,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="I44">
-        <f>D30-D31</f>
+        <f>D31-D32</f>
         <v/>
       </c>
       <c r="J44" t="n">
@@ -5416,11 +5439,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E33</t>
         </is>
       </c>
       <c r="I45">
-        <f>E30-E31</f>
+        <f>E31-E32</f>
         <v/>
       </c>
       <c r="J45" t="n">
@@ -5497,11 +5520,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>F32</t>
+          <t>F33</t>
         </is>
       </c>
       <c r="I46">
-        <f>F30-F31</f>
+        <f>F31-F32</f>
         <v/>
       </c>
       <c r="J46" t="n">
@@ -5578,11 +5601,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>B33</t>
+          <t>B34</t>
         </is>
       </c>
       <c r="I47">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",C$6:C$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",C$6:C$16)</f>
         <v/>
       </c>
       <c r="J47" t="n">
@@ -5654,11 +5677,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="I48">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",D$6:D$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",D$6:D$16)</f>
         <v/>
       </c>
       <c r="J48" t="n">
@@ -5730,11 +5753,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="I49">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",E$6:E$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",E$6:E$16)</f>
         <v/>
       </c>
       <c r="J49" t="n">
@@ -5806,11 +5829,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>E33</t>
+          <t>E34</t>
         </is>
       </c>
       <c r="I50">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",F$6:F$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",F$6:F$16)</f>
         <v/>
       </c>
       <c r="J50" t="n">
@@ -5882,11 +5905,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>F33</t>
+          <t>F34</t>
         </is>
       </c>
       <c r="I51">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",G$6:G$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",G$6:G$16)</f>
         <v/>
       </c>
       <c r="J51" t="n">
@@ -5958,11 +5981,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>B34</t>
+          <t>B35</t>
         </is>
       </c>
       <c r="I52">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",C$6:C$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",C$6:C$16)</f>
         <v/>
       </c>
       <c r="J52" t="n">
@@ -6034,11 +6057,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C35</t>
         </is>
       </c>
       <c r="I53">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",D$6:D$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",D$6:D$16)</f>
         <v/>
       </c>
       <c r="J53" t="n">
@@ -6110,11 +6133,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="I54">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",E$6:E$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",E$6:E$16)</f>
         <v/>
       </c>
       <c r="J54" t="n">
@@ -6186,11 +6209,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>E34</t>
+          <t>E35</t>
         </is>
       </c>
       <c r="I55">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",F$6:F$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",F$6:F$16)</f>
         <v/>
       </c>
       <c r="J55" t="n">
@@ -6262,11 +6285,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>F34</t>
+          <t>F35</t>
         </is>
       </c>
       <c r="I56">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",G$6:G$15)</f>
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",G$6:G$16)</f>
         <v/>
       </c>
       <c r="J56" t="n">
@@ -6338,11 +6361,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>B35</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="I57">
-        <f>B33-B34</f>
+        <f>B34-B35</f>
         <v/>
       </c>
       <c r="J57" t="n">
@@ -6419,11 +6442,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="I58">
-        <f>C33-C34</f>
+        <f>C34-C35</f>
         <v/>
       </c>
       <c r="J58" t="n">
@@ -6500,11 +6523,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="I59">
-        <f>D33-D34</f>
+        <f>D34-D35</f>
         <v/>
       </c>
       <c r="J59" t="n">
@@ -6581,11 +6604,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>E35</t>
+          <t>E36</t>
         </is>
       </c>
       <c r="I60">
-        <f>E33-E34</f>
+        <f>E34-E35</f>
         <v/>
       </c>
       <c r="J60" t="n">
@@ -6662,11 +6685,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>F35</t>
+          <t>F36</t>
         </is>
       </c>
       <c r="I61">
-        <f>F33-F34</f>
+        <f>F34-F35</f>
         <v/>
       </c>
       <c r="J61" t="n">
@@ -6743,11 +6766,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>B37</t>
         </is>
       </c>
       <c r="I62">
-        <f>B32+B35</f>
+        <f>B33+B36</f>
         <v/>
       </c>
       <c r="J62" t="n">
@@ -6824,11 +6847,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="I63">
-        <f>C32+C35</f>
+        <f>C33+C36</f>
         <v/>
       </c>
       <c r="J63" t="n">
@@ -6905,11 +6928,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="I64">
-        <f>D32+D35</f>
+        <f>D33+D36</f>
         <v/>
       </c>
       <c r="J64" t="n">
@@ -6986,11 +7009,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>E36</t>
+          <t>E37</t>
         </is>
       </c>
       <c r="I65">
-        <f>E32+E35</f>
+        <f>E33+E36</f>
         <v/>
       </c>
       <c r="J65" t="n">
@@ -7067,11 +7090,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>F36</t>
+          <t>F37</t>
         </is>
       </c>
       <c r="I66">
-        <f>F32+F35</f>
+        <f>F33+F36</f>
         <v/>
       </c>
       <c r="J66" t="n">
@@ -7148,11 +7171,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>B37</t>
+          <t>B38</t>
         </is>
       </c>
       <c r="I67">
-        <f>SUMIF($B$6:$B$15,"Financial Asset",C$6:C$15)</f>
+        <f>SUMIF($B$6:$B$16,"Financial Asset",C$6:C$16)</f>
         <v/>
       </c>
       <c r="J67" t="n">
@@ -7224,11 +7247,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="I68">
-        <f>SUMIF($B$6:$B$15,"Financial Asset",D$6:D$15)</f>
+        <f>SUMIF($B$6:$B$16,"Financial Asset",D$6:D$16)</f>
         <v/>
       </c>
       <c r="J68" t="n">
@@ -7300,11 +7323,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="I69">
-        <f>SUMIF($B$6:$B$15,"Financial Asset",E$6:E$15)</f>
+        <f>SUMIF($B$6:$B$16,"Financial Asset",E$6:E$16)</f>
         <v/>
       </c>
       <c r="J69" t="n">
@@ -7376,11 +7399,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>E37</t>
+          <t>E38</t>
         </is>
       </c>
       <c r="I70">
-        <f>SUMIF($B$6:$B$15,"Financial Asset",F$6:F$15)</f>
+        <f>SUMIF($B$6:$B$16,"Financial Asset",F$6:F$16)</f>
         <v/>
       </c>
       <c r="J70" t="n">
@@ -7452,11 +7475,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>F37</t>
+          <t>F38</t>
         </is>
       </c>
       <c r="I71">
-        <f>SUMIF($B$6:$B$15,"Financial Asset",G$6:G$15)</f>
+        <f>SUMIF($B$6:$B$16,"Financial Asset",G$6:G$16)</f>
         <v/>
       </c>
       <c r="J71" t="n">
@@ -7528,11 +7551,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>B38</t>
+          <t>B39</t>
         </is>
       </c>
       <c r="I72">
-        <f>SUMIF($B$6:$B$15,"Financial Liability",C$6:C$15)</f>
+        <f>SUMIF($B$6:$B$16,"Financial Liability",C$6:C$16)</f>
         <v/>
       </c>
       <c r="J72" t="n">
@@ -7604,11 +7627,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="I73">
-        <f>SUMIF($B$6:$B$15,"Financial Liability",D$6:D$15)</f>
+        <f>SUMIF($B$6:$B$16,"Financial Liability",D$6:D$16)</f>
         <v/>
       </c>
       <c r="J73" t="n">
@@ -7680,11 +7703,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>D38</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="I74">
-        <f>SUMIF($B$6:$B$15,"Financial Liability",E$6:E$15)</f>
+        <f>SUMIF($B$6:$B$16,"Financial Liability",E$6:E$16)</f>
         <v/>
       </c>
       <c r="J74" t="n">
@@ -7756,11 +7779,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>E38</t>
+          <t>E39</t>
         </is>
       </c>
       <c r="I75">
-        <f>SUMIF($B$6:$B$15,"Financial Liability",F$6:F$15)</f>
+        <f>SUMIF($B$6:$B$16,"Financial Liability",F$6:F$16)</f>
         <v/>
       </c>
       <c r="J75" t="n">
@@ -7832,11 +7855,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>F38</t>
+          <t>F39</t>
         </is>
       </c>
       <c r="I76">
-        <f>SUMIF($B$6:$B$15,"Financial Liability",G$6:G$15)</f>
+        <f>SUMIF($B$6:$B$16,"Financial Liability",G$6:G$16)</f>
         <v/>
       </c>
       <c r="J76" t="n">
@@ -7908,11 +7931,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>B39</t>
+          <t>B40</t>
         </is>
       </c>
       <c r="I77">
-        <f>B38-B37</f>
+        <f>B39-B38</f>
         <v/>
       </c>
       <c r="J77" t="n">
@@ -7989,11 +8012,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="I78">
-        <f>C38-C37</f>
+        <f>C39-C38</f>
         <v/>
       </c>
       <c r="J78" t="n">
@@ -8070,11 +8093,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>D40</t>
         </is>
       </c>
       <c r="I79">
-        <f>D38-D37</f>
+        <f>D39-D38</f>
         <v/>
       </c>
       <c r="J79" t="n">
@@ -8151,11 +8174,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>E39</t>
+          <t>E40</t>
         </is>
       </c>
       <c r="I80">
-        <f>E38-E37</f>
+        <f>E39-E38</f>
         <v/>
       </c>
       <c r="J80" t="n">
@@ -8232,11 +8255,11 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>F39</t>
+          <t>F40</t>
         </is>
       </c>
       <c r="I81">
-        <f>F38-F37</f>
+        <f>F39-F38</f>
         <v/>
       </c>
       <c r="J81" t="n">
@@ -8313,11 +8336,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>B40</t>
+          <t>B41</t>
         </is>
       </c>
       <c r="I82">
-        <f>B36-B39</f>
+        <f>B37-B40</f>
         <v/>
       </c>
       <c r="J82" t="n">
@@ -8394,11 +8417,11 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>C41</t>
         </is>
       </c>
       <c r="I83">
-        <f>C36-C39</f>
+        <f>C37-C40</f>
         <v/>
       </c>
       <c r="J83" t="n">
@@ -8475,11 +8498,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>D40</t>
+          <t>D41</t>
         </is>
       </c>
       <c r="I84">
-        <f>D36-D39</f>
+        <f>D37-D40</f>
         <v/>
       </c>
       <c r="J84" t="n">
@@ -8556,11 +8579,11 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>E40</t>
+          <t>E41</t>
         </is>
       </c>
       <c r="I85">
-        <f>E36-E39</f>
+        <f>E37-E40</f>
         <v/>
       </c>
       <c r="J85" t="n">
@@ -8637,11 +8660,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>F40</t>
+          <t>F41</t>
         </is>
       </c>
       <c r="I86">
-        <f>F36-F39</f>
+        <f>F37-F40</f>
         <v/>
       </c>
       <c r="J86" t="n">
@@ -8722,7 +8745,7 @@
         </is>
       </c>
       <c r="I87">
-        <f>IF('Condensed Financials'!B18=0,0,'Condensed Financials'!C18/'Condensed Financials'!B18-1)</f>
+        <f>IF('Condensed Financials'!B19=0,0,'Condensed Financials'!C19/'Condensed Financials'!B19-1)</f>
         <v/>
       </c>
       <c r="J87" t="n">
@@ -8803,7 +8826,7 @@
         </is>
       </c>
       <c r="I88">
-        <f>IF('Condensed Financials'!C18=0,0,'Condensed Financials'!D18/'Condensed Financials'!C18-1)</f>
+        <f>IF('Condensed Financials'!C19=0,0,'Condensed Financials'!D19/'Condensed Financials'!C19-1)</f>
         <v/>
       </c>
       <c r="J88" t="n">
@@ -8884,7 +8907,7 @@
         </is>
       </c>
       <c r="I89">
-        <f>IF('Condensed Financials'!D18=0,0,'Condensed Financials'!E18/'Condensed Financials'!D18-1)</f>
+        <f>IF('Condensed Financials'!D19=0,0,'Condensed Financials'!E19/'Condensed Financials'!D19-1)</f>
         <v/>
       </c>
       <c r="J89" t="n">
@@ -8965,7 +8988,7 @@
         </is>
       </c>
       <c r="I90">
-        <f>IF('Condensed Financials'!E18=0,0,'Condensed Financials'!F18/'Condensed Financials'!E18-1)</f>
+        <f>IF('Condensed Financials'!E19=0,0,'Condensed Financials'!F19/'Condensed Financials'!E19-1)</f>
         <v/>
       </c>
       <c r="J90" t="n">
@@ -9046,7 +9069,7 @@
         </is>
       </c>
       <c r="I91">
-        <f>IF('Condensed Financials'!B18=0,0,'Condensed Financials'!B27/'Condensed Financials'!B18)</f>
+        <f>IF('Condensed Financials'!B19=0,0,'Condensed Financials'!B28/'Condensed Financials'!B19)</f>
         <v/>
       </c>
       <c r="J91" t="n">
@@ -9127,7 +9150,7 @@
         </is>
       </c>
       <c r="I92">
-        <f>IF('Condensed Financials'!C18=0,0,'Condensed Financials'!C27/'Condensed Financials'!C18)</f>
+        <f>IF('Condensed Financials'!C19=0,0,'Condensed Financials'!C28/'Condensed Financials'!C19)</f>
         <v/>
       </c>
       <c r="J92" t="n">
@@ -9208,7 +9231,7 @@
         </is>
       </c>
       <c r="I93">
-        <f>IF('Condensed Financials'!D18=0,0,'Condensed Financials'!D27/'Condensed Financials'!D18)</f>
+        <f>IF('Condensed Financials'!D19=0,0,'Condensed Financials'!D28/'Condensed Financials'!D19)</f>
         <v/>
       </c>
       <c r="J93" t="n">
@@ -9289,7 +9312,7 @@
         </is>
       </c>
       <c r="I94">
-        <f>IF('Condensed Financials'!E18=0,0,'Condensed Financials'!E27/'Condensed Financials'!E18)</f>
+        <f>IF('Condensed Financials'!E19=0,0,'Condensed Financials'!E28/'Condensed Financials'!E19)</f>
         <v/>
       </c>
       <c r="J94" t="n">
@@ -9370,7 +9393,7 @@
         </is>
       </c>
       <c r="I95">
-        <f>IF('Condensed Financials'!F18=0,0,'Condensed Financials'!F27/'Condensed Financials'!F18)</f>
+        <f>IF('Condensed Financials'!F19=0,0,'Condensed Financials'!F28/'Condensed Financials'!F19)</f>
         <v/>
       </c>
       <c r="J95" t="n">
@@ -9451,7 +9474,7 @@
         </is>
       </c>
       <c r="I96">
-        <f>IF((('Condensed Financials'!C36+'Condensed Financials'!B36)/2)=0,0,'Condensed Financials'!C27/(('Condensed Financials'!C36+'Condensed Financials'!B36)/2))</f>
+        <f>IF((('Condensed Financials'!C37+'Condensed Financials'!B37)/2)=0,0,'Condensed Financials'!C28/(('Condensed Financials'!C37+'Condensed Financials'!B37)/2))</f>
         <v/>
       </c>
       <c r="J96" t="n">
@@ -9532,7 +9555,7 @@
         </is>
       </c>
       <c r="I97">
-        <f>IF((('Condensed Financials'!D36+'Condensed Financials'!C36)/2)=0,0,'Condensed Financials'!D27/(('Condensed Financials'!D36+'Condensed Financials'!C36)/2))</f>
+        <f>IF((('Condensed Financials'!D37+'Condensed Financials'!C37)/2)=0,0,'Condensed Financials'!D28/(('Condensed Financials'!D37+'Condensed Financials'!C37)/2))</f>
         <v/>
       </c>
       <c r="J97" t="n">
@@ -9613,7 +9636,7 @@
         </is>
       </c>
       <c r="I98">
-        <f>IF((('Condensed Financials'!E36+'Condensed Financials'!D36)/2)=0,0,'Condensed Financials'!E27/(('Condensed Financials'!E36+'Condensed Financials'!D36)/2))</f>
+        <f>IF((('Condensed Financials'!E37+'Condensed Financials'!D37)/2)=0,0,'Condensed Financials'!E28/(('Condensed Financials'!E37+'Condensed Financials'!D37)/2))</f>
         <v/>
       </c>
       <c r="J98" t="n">
@@ -9694,7 +9717,7 @@
         </is>
       </c>
       <c r="I99">
-        <f>IF((('Condensed Financials'!F36+'Condensed Financials'!E36)/2)=0,0,'Condensed Financials'!F27/(('Condensed Financials'!F36+'Condensed Financials'!E36)/2))</f>
+        <f>IF((('Condensed Financials'!F37+'Condensed Financials'!E37)/2)=0,0,'Condensed Financials'!F28/(('Condensed Financials'!F37+'Condensed Financials'!E37)/2))</f>
         <v/>
       </c>
       <c r="J99" t="n">
@@ -9775,7 +9798,7 @@
         </is>
       </c>
       <c r="I100">
-        <f>IF((('Condensed Financials'!C39+'Condensed Financials'!B39)/2)=0,0,'Condensed Financials'!C26/(('Condensed Financials'!C39+'Condensed Financials'!B39)/2))</f>
+        <f>IF((('Condensed Financials'!C40+'Condensed Financials'!B40)/2)=0,0,'Condensed Financials'!C27/(('Condensed Financials'!C40+'Condensed Financials'!B40)/2))</f>
         <v/>
       </c>
       <c r="J100" t="n">
@@ -9856,7 +9879,7 @@
         </is>
       </c>
       <c r="I101">
-        <f>IF((('Condensed Financials'!D39+'Condensed Financials'!C39)/2)=0,0,'Condensed Financials'!D26/(('Condensed Financials'!D39+'Condensed Financials'!C39)/2))</f>
+        <f>IF((('Condensed Financials'!D40+'Condensed Financials'!C40)/2)=0,0,'Condensed Financials'!D27/(('Condensed Financials'!D40+'Condensed Financials'!C40)/2))</f>
         <v/>
       </c>
       <c r="J101" t="n">
@@ -9937,7 +9960,7 @@
         </is>
       </c>
       <c r="I102">
-        <f>IF((('Condensed Financials'!E39+'Condensed Financials'!D39)/2)=0,0,'Condensed Financials'!E26/(('Condensed Financials'!E39+'Condensed Financials'!D39)/2))</f>
+        <f>IF((('Condensed Financials'!E40+'Condensed Financials'!D40)/2)=0,0,'Condensed Financials'!E27/(('Condensed Financials'!E40+'Condensed Financials'!D40)/2))</f>
         <v/>
       </c>
       <c r="J102" t="n">
@@ -10018,7 +10041,7 @@
         </is>
       </c>
       <c r="I103">
-        <f>IF((('Condensed Financials'!F39+'Condensed Financials'!E39)/2)=0,0,'Condensed Financials'!F26/(('Condensed Financials'!F39+'Condensed Financials'!E39)/2))</f>
+        <f>IF((('Condensed Financials'!F40+'Condensed Financials'!E40)/2)=0,0,'Condensed Financials'!F27/(('Condensed Financials'!F40+'Condensed Financials'!E40)/2))</f>
         <v/>
       </c>
       <c r="J103" t="n">
@@ -10423,7 +10446,7 @@
         </is>
       </c>
       <c r="I108">
-        <f>IF((('Condensed Financials'!C40+'Condensed Financials'!B40)/2)=0,0,(('Condensed Financials'!C39+'Condensed Financials'!B39)/2)/(('Condensed Financials'!C40+'Condensed Financials'!B40)/2))</f>
+        <f>IF((('Condensed Financials'!C41+'Condensed Financials'!B41)/2)=0,0,(('Condensed Financials'!C40+'Condensed Financials'!B40)/2)/(('Condensed Financials'!C41+'Condensed Financials'!B41)/2))</f>
         <v/>
       </c>
       <c r="J108" t="n">
@@ -10504,7 +10527,7 @@
         </is>
       </c>
       <c r="I109">
-        <f>IF((('Condensed Financials'!D40+'Condensed Financials'!C40)/2)=0,0,(('Condensed Financials'!D39+'Condensed Financials'!C39)/2)/(('Condensed Financials'!D40+'Condensed Financials'!C40)/2))</f>
+        <f>IF((('Condensed Financials'!D41+'Condensed Financials'!C41)/2)=0,0,(('Condensed Financials'!D40+'Condensed Financials'!C40)/2)/(('Condensed Financials'!D41+'Condensed Financials'!C41)/2))</f>
         <v/>
       </c>
       <c r="J109" t="n">
@@ -10585,7 +10608,7 @@
         </is>
       </c>
       <c r="I110">
-        <f>IF((('Condensed Financials'!E40+'Condensed Financials'!D40)/2)=0,0,(('Condensed Financials'!E39+'Condensed Financials'!D39)/2)/(('Condensed Financials'!E40+'Condensed Financials'!D40)/2))</f>
+        <f>IF((('Condensed Financials'!E41+'Condensed Financials'!D41)/2)=0,0,(('Condensed Financials'!E40+'Condensed Financials'!D40)/2)/(('Condensed Financials'!E41+'Condensed Financials'!D41)/2))</f>
         <v/>
       </c>
       <c r="J110" t="n">
@@ -10666,7 +10689,7 @@
         </is>
       </c>
       <c r="I111">
-        <f>IF((('Condensed Financials'!F40+'Condensed Financials'!E40)/2)=0,0,(('Condensed Financials'!F39+'Condensed Financials'!E39)/2)/(('Condensed Financials'!F40+'Condensed Financials'!E40)/2))</f>
+        <f>IF((('Condensed Financials'!F41+'Condensed Financials'!E41)/2)=0,0,(('Condensed Financials'!F40+'Condensed Financials'!E40)/2)/(('Condensed Financials'!F41+'Condensed Financials'!E41)/2))</f>
         <v/>
       </c>
       <c r="J111" t="n">
@@ -11071,7 +11094,7 @@
         </is>
       </c>
       <c r="I116">
-        <f>IF((('Condensed Financials'!C40+'Condensed Financials'!B40)/2)=0,0,'Condensed Financials'!C19/(('Condensed Financials'!C40+'Condensed Financials'!B40)/2))</f>
+        <f>IF((('Condensed Financials'!C41+'Condensed Financials'!B41)/2)=0,0,'Condensed Financials'!C20/(('Condensed Financials'!C41+'Condensed Financials'!B41)/2))</f>
         <v/>
       </c>
       <c r="J116" t="n">
@@ -11152,7 +11175,7 @@
         </is>
       </c>
       <c r="I117">
-        <f>IF((('Condensed Financials'!D40+'Condensed Financials'!C40)/2)=0,0,'Condensed Financials'!D19/(('Condensed Financials'!D40+'Condensed Financials'!C40)/2))</f>
+        <f>IF((('Condensed Financials'!D41+'Condensed Financials'!C41)/2)=0,0,'Condensed Financials'!D20/(('Condensed Financials'!D41+'Condensed Financials'!C41)/2))</f>
         <v/>
       </c>
       <c r="J117" t="n">
@@ -11233,7 +11256,7 @@
         </is>
       </c>
       <c r="I118">
-        <f>IF((('Condensed Financials'!E40+'Condensed Financials'!D40)/2)=0,0,'Condensed Financials'!E19/(('Condensed Financials'!E40+'Condensed Financials'!D40)/2))</f>
+        <f>IF((('Condensed Financials'!E41+'Condensed Financials'!D41)/2)=0,0,'Condensed Financials'!E20/(('Condensed Financials'!E41+'Condensed Financials'!D41)/2))</f>
         <v/>
       </c>
       <c r="J118" t="n">
@@ -11314,7 +11337,7 @@
         </is>
       </c>
       <c r="I119">
-        <f>IF((('Condensed Financials'!F40+'Condensed Financials'!E40)/2)=0,0,'Condensed Financials'!F19/(('Condensed Financials'!F40+'Condensed Financials'!E40)/2))</f>
+        <f>IF((('Condensed Financials'!F41+'Condensed Financials'!E41)/2)=0,0,'Condensed Financials'!F20/(('Condensed Financials'!F41+'Condensed Financials'!E41)/2))</f>
         <v/>
       </c>
       <c r="J119" t="n">
@@ -11378,28 +11401,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Company: Demo Holdings Limited (DEMO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Statement: Income Statement</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Units: HKD in Millions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Source: manual ingestion (HK)</t>
         </is>
@@ -11407,244 +11430,244 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>8500</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>9200</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>10100</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>11200</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="14" t="n">
         <v>12500</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Cost of sales</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="15" t="n">
         <v>-3400</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>-3680</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>-4040</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>-4480</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <v>-5000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="15" t="n">
         <v>5100</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="15" t="n">
         <v>5520</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>6060</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>6720</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>7500</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Administrative expenses</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="15" t="n">
         <v>-1700</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="15" t="n">
         <v>-1840</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>-2020</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>-2240</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <v>-2500</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Operating profit</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="15" t="n">
         <v>3400</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="15" t="n">
         <v>3680</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>4040</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>4480</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Finance costs</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="15" t="n">
         <v>-120</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="15" t="n">
         <v>-130</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>-140</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>-150</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="15" t="n">
         <v>-160</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Finance income</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="15" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="15" t="n">
         <v>3325</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="15" t="n">
         <v>3600</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>3955</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <v>4390</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="15" t="n">
         <v>4905</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Income tax expense</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="15" t="n">
         <v>-565</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="15" t="n">
         <v>-612</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <v>-672</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <v>-746</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="15" t="n">
         <v>-833</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="15" t="n">
         <v>2760</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="15" t="n">
         <v>2988</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="15" t="n">
         <v>3283</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="15" t="n">
         <v>3644</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="15" t="n">
         <v>4072</v>
       </c>
     </row>
@@ -11659,7 +11682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -11671,28 +11694,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Company: Demo Holdings Limited (DEMO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Statement: Balance Sheet</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Units: HKD in Millions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Source: manual ingestion (HK)</t>
         </is>
@@ -11700,310 +11723,332 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>1350</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>1680</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <v>1850</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Trade receivables</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="15" t="n">
         <v>850</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>920</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>1010</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>1120</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>680</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>736</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>808</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>896</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="14" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="15" t="n">
         <v>3200</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="15" t="n">
         <v>3400</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>3600</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>3800</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="14" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Other non-current assets</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="15" t="n">
         <v>1670</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="15" t="n">
         <v>1894</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>2282</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>2804</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="15" t="n">
         <v>3500</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="15" t="n">
         <v>8500</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="15" t="n">
         <v>9200</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>10100</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="15" t="n">
         <v>11200</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="15" t="n">
         <v>12500</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Trade payables</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="15" t="n">
         <v>595</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="15" t="n">
         <v>644</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>707</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <v>784</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="15" t="n">
         <v>875</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Bank borrowings</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="15" t="n">
         <v>1400</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <v>1300</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="15" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Operating lease liabilities</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>320</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>340</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>360</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Other non-current liabilities</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>1305</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>1456</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>1593</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>1716</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="B17" s="15" t="n">
+        <v>1005</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>1136</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>1253</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>1356</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B18" s="15" t="n">
         <v>3400</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C18" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D18" s="15" t="n">
         <v>3600</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E18" s="15" t="n">
         <v>3700</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F18" s="15" t="n">
         <v>3800</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Share capital and reserves</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B19" s="15" t="n">
         <v>5100</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C19" s="15" t="n">
         <v>5700</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D19" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E19" s="15" t="n">
         <v>7500</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F19" s="15" t="n">
         <v>8700</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Total equity</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B20" s="15" t="n">
         <v>5100</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C20" s="15" t="n">
         <v>5700</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D20" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E20" s="15" t="n">
         <v>7500</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F20" s="15" t="n">
         <v>8700</v>
       </c>
     </row>
@@ -12030,28 +12075,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Company: Demo Holdings Limited (DEMO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Statement: Cash Flow Statement</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Units: HKD in Millions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Source: manual ingestion (HK)</t>
         </is>
@@ -12059,156 +12104,156 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="15" t="n">
         <v>2760</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>2988</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>3283</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>3644</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <v>4072</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="15" t="n">
         <v>340</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>368</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>404</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>448</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Net cash from operating activities</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="15" t="n">
         <v>1450</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="15" t="n">
         <v>1600</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>1750</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>1930</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>2070</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Net cash used in investing activities</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="15" t="n">
         <v>-800</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="15" t="n">
         <v>-850</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>-900</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>-950</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <v>-1000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Net cash from financing activities</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="15" t="n">
         <v>-500</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="15" t="n">
         <v>-600</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>-700</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>-800</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>-900</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Net change in cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>180</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="15" t="n">
         <v>170</v>
       </c>
     </row>
@@ -12223,7 +12268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -12237,7 +12282,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Demo Holdings Limited (DEMO) — Condensed Financials</t>
         </is>
@@ -12246,996 +12291,1028 @@
     <row r="2"/>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>BALANCE SHEET CLASSIFICATION</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="13" t="n">
         <v>46022</v>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Financial Asset</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>1350</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="15" t="n">
         <v>1680</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="15" t="n">
         <v>1850</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Trade receivables</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Operating Working Capital Asset</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>850</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>920</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>1010</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <v>1120</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="15" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Operating Working Capital Asset</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>680</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>736</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>808</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <v>896</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Operating Long-Term Asset</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="15" t="n">
         <v>3200</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>3400</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>3600</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>3800</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="15" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Operating Long-Term Asset</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="14" t="n">
         <v>900</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="14" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Other non-current assets</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Operating Long-Term Asset</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="15" t="n">
         <v>1670</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>1894</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>2282</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>2804</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="15" t="n">
         <v>3500</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Trade payables</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Operating Working Capital Liability</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="15" t="n">
         <v>595</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>644</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>707</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="15" t="n">
         <v>784</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="15" t="n">
         <v>875</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Bank borrowings</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Financial Liability</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>1400</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="15" t="n">
         <v>1300</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="15" t="n">
         <v>1100</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Operating lease liabilities</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Operating Long-Term Liability</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>320</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>340</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>360</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>380</v>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>⚠ Review: Lease liability concept — operating vs financial judgment</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Other non-current liabilities</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Operating Long-Term Liability</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
-        <v>1305</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>1456</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>1593</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>1716</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="C15" s="15" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>1136</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>1253</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>1356</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Share capital and reserves</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C16" s="15" t="n">
         <v>5100</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D16" s="15" t="n">
         <v>5700</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E16" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F16" s="15" t="n">
         <v>7500</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G16" s="15" t="n">
         <v>8700</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>CONDENSED INCOME STATEMENT</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C18" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E18" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F18" s="13" t="n">
         <v>46022</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B18" s="15">
+      <c r="B19" s="16">
         <f>'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C18" s="15">
+      <c r="C19" s="16">
         <f>'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D18" s="15">
+      <c r="D19" s="16">
         <f>'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E19" s="16">
         <f>'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F18" s="15">
+      <c r="F19" s="16">
         <f>'Income Statement'!F7</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B19" s="16">
+      <c r="B20" s="17">
         <f>'Income Statement'!B16</f>
         <v/>
       </c>
-      <c r="C19" s="16">
+      <c r="C20" s="17">
         <f>'Income Statement'!C16</f>
         <v/>
       </c>
-      <c r="D19" s="16">
+      <c r="D20" s="17">
         <f>'Income Statement'!D16</f>
         <v/>
       </c>
-      <c r="E19" s="16">
+      <c r="E20" s="17">
         <f>'Income Statement'!E16</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F20" s="17">
         <f>'Income Statement'!F16</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B20" s="11">
+      <c r="B21" s="12">
         <f>'Income Statement'!B14</f>
         <v/>
       </c>
-      <c r="C20" s="11">
+      <c r="C21" s="12">
         <f>'Income Statement'!C14</f>
         <v/>
       </c>
-      <c r="D20" s="11">
+      <c r="D21" s="12">
         <f>'Income Statement'!D14</f>
         <v/>
       </c>
-      <c r="E20" s="11">
+      <c r="E21" s="12">
         <f>'Income Statement'!E14</f>
         <v/>
       </c>
-      <c r="F20" s="11">
+      <c r="F21" s="12">
         <f>'Income Statement'!F14</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Tax Expense</t>
         </is>
       </c>
-      <c r="B21" s="11">
+      <c r="B22" s="12">
         <f>'Income Statement'!B15</f>
         <v/>
       </c>
-      <c r="C21" s="11">
+      <c r="C22" s="12">
         <f>'Income Statement'!C15</f>
         <v/>
       </c>
-      <c r="D21" s="11">
+      <c r="D22" s="12">
         <f>'Income Statement'!D15</f>
         <v/>
       </c>
-      <c r="E21" s="11">
+      <c r="E22" s="12">
         <f>'Income Statement'!E15</f>
         <v/>
       </c>
-      <c r="F21" s="11">
+      <c r="F22" s="12">
         <f>'Income Statement'!F15</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B22" s="11">
+      <c r="B23" s="12">
         <f>'Income Statement'!B12</f>
         <v/>
       </c>
-      <c r="C22" s="11">
+      <c r="C23" s="12">
         <f>'Income Statement'!C12</f>
         <v/>
       </c>
-      <c r="D22" s="11">
+      <c r="D23" s="12">
         <f>'Income Statement'!D12</f>
         <v/>
       </c>
-      <c r="E22" s="11">
+      <c r="E23" s="12">
         <f>'Income Statement'!E12</f>
         <v/>
       </c>
-      <c r="F22" s="11">
+      <c r="F23" s="12">
         <f>'Income Statement'!F12</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B23" s="11">
+      <c r="B24" s="12">
         <f>'Income Statement'!B13</f>
         <v/>
       </c>
-      <c r="C23" s="11">
+      <c r="C24" s="12">
         <f>'Income Statement'!C13</f>
         <v/>
       </c>
-      <c r="D23" s="11">
+      <c r="D24" s="12">
         <f>'Income Statement'!D13</f>
         <v/>
       </c>
-      <c r="E23" s="11">
+      <c r="E24" s="12">
         <f>'Income Statement'!E13</f>
         <v/>
       </c>
-      <c r="F23" s="11">
+      <c r="F24" s="12">
         <f>'Income Statement'!F13</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Effective Tax Rate</t>
         </is>
       </c>
-      <c r="B24" s="17">
-        <f>IF(B20=0,0,-B21/B20)</f>
-        <v/>
-      </c>
-      <c r="C24" s="17">
-        <f>IF(C20=0,0,-C21/C20)</f>
-        <v/>
-      </c>
-      <c r="D24" s="17">
-        <f>IF(D20=0,0,-D21/D20)</f>
-        <v/>
-      </c>
-      <c r="E24" s="17">
-        <f>IF(E20=0,0,-E21/E20)</f>
-        <v/>
-      </c>
-      <c r="F24" s="17">
-        <f>IF(F20=0,0,-F21/F20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="B25" s="18">
+        <f>IF(B21=0,0,-B22/B21)</f>
+        <v/>
+      </c>
+      <c r="C25" s="18">
+        <f>IF(C21=0,0,-C22/C21)</f>
+        <v/>
+      </c>
+      <c r="D25" s="18">
+        <f>IF(D21=0,0,-D22/D21)</f>
+        <v/>
+      </c>
+      <c r="E25" s="18">
+        <f>IF(E21=0,0,-E22/E21)</f>
+        <v/>
+      </c>
+      <c r="F25" s="18">
+        <f>IF(F21=0,0,-F22/F21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Net Interest</t>
         </is>
       </c>
-      <c r="B25" s="18">
-        <f>-(B22+B23)</f>
-        <v/>
-      </c>
-      <c r="C25" s="18">
-        <f>-(C22+C23)</f>
-        <v/>
-      </c>
-      <c r="D25" s="18">
-        <f>-(D22+D23)</f>
-        <v/>
-      </c>
-      <c r="E25" s="18">
-        <f>-(E22+E23)</f>
-        <v/>
-      </c>
-      <c r="F25" s="18">
-        <f>-(F22+F23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="B26" s="19">
+        <f>-(B23+B24)</f>
+        <v/>
+      </c>
+      <c r="C26" s="19">
+        <f>-(C23+C24)</f>
+        <v/>
+      </c>
+      <c r="D26" s="19">
+        <f>-(D23+D24)</f>
+        <v/>
+      </c>
+      <c r="E26" s="19">
+        <f>-(E23+E24)</f>
+        <v/>
+      </c>
+      <c r="F26" s="19">
+        <f>-(F23+F24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Net Interest After Tax</t>
         </is>
       </c>
-      <c r="B26" s="18">
-        <f>B25*(1-B24)</f>
-        <v/>
-      </c>
-      <c r="C26" s="18">
-        <f>C25*(1-C24)</f>
-        <v/>
-      </c>
-      <c r="D26" s="18">
-        <f>D25*(1-D24)</f>
-        <v/>
-      </c>
-      <c r="E26" s="18">
-        <f>E25*(1-E24)</f>
-        <v/>
-      </c>
-      <c r="F26" s="18">
-        <f>F25*(1-F24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="B27" s="19">
+        <f>B26*(1-B25)</f>
+        <v/>
+      </c>
+      <c r="C27" s="19">
+        <f>C26*(1-C25)</f>
+        <v/>
+      </c>
+      <c r="D27" s="19">
+        <f>D26*(1-D25)</f>
+        <v/>
+      </c>
+      <c r="E27" s="19">
+        <f>E26*(1-E25)</f>
+        <v/>
+      </c>
+      <c r="F27" s="19">
+        <f>F26*(1-F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B27" s="20">
-        <f>B19+B26</f>
-        <v/>
-      </c>
-      <c r="C27" s="20">
-        <f>C19+C26</f>
-        <v/>
-      </c>
-      <c r="D27" s="20">
-        <f>D19+D26</f>
-        <v/>
-      </c>
-      <c r="E27" s="20">
-        <f>E19+E26</f>
-        <v/>
-      </c>
-      <c r="F27" s="20">
-        <f>F19+F26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="B28" s="21">
+        <f>B20+B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="21">
+        <f>C20+C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="21">
+        <f>D20+D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="21">
+        <f>E20+E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="21">
+        <f>F20+F27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>CONDENSED BALANCE SHEET</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Operating Working Capital Assets</t>
         </is>
       </c>
-      <c r="B30" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",C$6:C$15)</f>
-        <v/>
-      </c>
-      <c r="C30" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",D$6:D$15)</f>
-        <v/>
-      </c>
-      <c r="D30" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",E$6:E$15)</f>
-        <v/>
-      </c>
-      <c r="E30" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",F$6:F$15)</f>
-        <v/>
-      </c>
-      <c r="F30" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Asset",G$6:G$15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="B31" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",C$6:C$16)</f>
+        <v/>
+      </c>
+      <c r="C31" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",D$6:D$16)</f>
+        <v/>
+      </c>
+      <c r="D31" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",E$6:E$16)</f>
+        <v/>
+      </c>
+      <c r="E31" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",F$6:F$16)</f>
+        <v/>
+      </c>
+      <c r="F31" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Asset",G$6:G$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Operating Working Capital Liabilities</t>
         </is>
       </c>
-      <c r="B31" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",C$6:C$15)</f>
-        <v/>
-      </c>
-      <c r="C31" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",D$6:D$15)</f>
-        <v/>
-      </c>
-      <c r="D31" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",E$6:E$15)</f>
-        <v/>
-      </c>
-      <c r="E31" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",F$6:F$15)</f>
-        <v/>
-      </c>
-      <c r="F31" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Working Capital Liability",G$6:G$15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="B32" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",C$6:C$16)</f>
+        <v/>
+      </c>
+      <c r="C32" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",D$6:D$16)</f>
+        <v/>
+      </c>
+      <c r="D32" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",E$6:E$16)</f>
+        <v/>
+      </c>
+      <c r="E32" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",F$6:F$16)</f>
+        <v/>
+      </c>
+      <c r="F32" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Working Capital Liability",G$6:G$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>NOWC</t>
         </is>
       </c>
-      <c r="B32" s="20">
-        <f>B30-B31</f>
-        <v/>
-      </c>
-      <c r="C32" s="20">
-        <f>C30-C31</f>
-        <v/>
-      </c>
-      <c r="D32" s="20">
-        <f>D30-D31</f>
-        <v/>
-      </c>
-      <c r="E32" s="20">
-        <f>E30-E31</f>
-        <v/>
-      </c>
-      <c r="F32" s="20">
-        <f>F30-F31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="B33" s="21">
+        <f>B31-B32</f>
+        <v/>
+      </c>
+      <c r="C33" s="21">
+        <f>C31-C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="21">
+        <f>D31-D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="21">
+        <f>E31-E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="21">
+        <f>F31-F32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Operating Long-Term Assets</t>
         </is>
       </c>
-      <c r="B33" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",C$6:C$15)</f>
-        <v/>
-      </c>
-      <c r="C33" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",D$6:D$15)</f>
-        <v/>
-      </c>
-      <c r="D33" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",E$6:E$15)</f>
-        <v/>
-      </c>
-      <c r="E33" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",F$6:F$15)</f>
-        <v/>
-      </c>
-      <c r="F33" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Asset",G$6:G$15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="B34" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",C$6:C$16)</f>
+        <v/>
+      </c>
+      <c r="C34" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",D$6:D$16)</f>
+        <v/>
+      </c>
+      <c r="D34" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",E$6:E$16)</f>
+        <v/>
+      </c>
+      <c r="E34" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",F$6:F$16)</f>
+        <v/>
+      </c>
+      <c r="F34" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Asset",G$6:G$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Operating Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B34" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",C$6:C$15)</f>
-        <v/>
-      </c>
-      <c r="C34" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",D$6:D$15)</f>
-        <v/>
-      </c>
-      <c r="D34" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",E$6:E$15)</f>
-        <v/>
-      </c>
-      <c r="E34" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",F$6:F$15)</f>
-        <v/>
-      </c>
-      <c r="F34" s="18">
-        <f>SUMIF($B$6:$B$15,"Operating Long-Term Liability",G$6:G$15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="B35" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",C$6:C$16)</f>
+        <v/>
+      </c>
+      <c r="C35" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",D$6:D$16)</f>
+        <v/>
+      </c>
+      <c r="D35" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",E$6:E$16)</f>
+        <v/>
+      </c>
+      <c r="E35" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",F$6:F$16)</f>
+        <v/>
+      </c>
+      <c r="F35" s="19">
+        <f>SUMIF($B$6:$B$16,"Operating Long-Term Liability",G$6:G$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>NOLA</t>
         </is>
       </c>
-      <c r="B35" s="20">
-        <f>B33-B34</f>
-        <v/>
-      </c>
-      <c r="C35" s="20">
-        <f>C33-C34</f>
-        <v/>
-      </c>
-      <c r="D35" s="20">
-        <f>D33-D34</f>
-        <v/>
-      </c>
-      <c r="E35" s="20">
-        <f>E33-E34</f>
-        <v/>
-      </c>
-      <c r="F35" s="20">
-        <f>F33-F34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="B36" s="21">
+        <f>B34-B35</f>
+        <v/>
+      </c>
+      <c r="C36" s="21">
+        <f>C34-C35</f>
+        <v/>
+      </c>
+      <c r="D36" s="21">
+        <f>D34-D35</f>
+        <v/>
+      </c>
+      <c r="E36" s="21">
+        <f>E34-E35</f>
+        <v/>
+      </c>
+      <c r="F36" s="21">
+        <f>F34-F35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>NOA</t>
         </is>
       </c>
-      <c r="B36" s="20">
-        <f>B32+B35</f>
-        <v/>
-      </c>
-      <c r="C36" s="20">
-        <f>C32+C35</f>
-        <v/>
-      </c>
-      <c r="D36" s="20">
-        <f>D32+D35</f>
-        <v/>
-      </c>
-      <c r="E36" s="20">
-        <f>E32+E35</f>
-        <v/>
-      </c>
-      <c r="F36" s="20">
-        <f>F32+F35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B37" s="21">
+        <f>B33+B36</f>
+        <v/>
+      </c>
+      <c r="C37" s="21">
+        <f>C33+C36</f>
+        <v/>
+      </c>
+      <c r="D37" s="21">
+        <f>D33+D36</f>
+        <v/>
+      </c>
+      <c r="E37" s="21">
+        <f>E33+E36</f>
+        <v/>
+      </c>
+      <c r="F37" s="21">
+        <f>F33+F36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Financial Assets</t>
         </is>
       </c>
-      <c r="B37" s="18">
-        <f>SUMIF($B$6:$B$15,"Financial Asset",C$6:C$15)</f>
-        <v/>
-      </c>
-      <c r="C37" s="18">
-        <f>SUMIF($B$6:$B$15,"Financial Asset",D$6:D$15)</f>
-        <v/>
-      </c>
-      <c r="D37" s="18">
-        <f>SUMIF($B$6:$B$15,"Financial Asset",E$6:E$15)</f>
-        <v/>
-      </c>
-      <c r="E37" s="18">
-        <f>SUMIF($B$6:$B$15,"Financial Asset",F$6:F$15)</f>
-        <v/>
-      </c>
-      <c r="F37" s="18">
-        <f>SUMIF($B$6:$B$15,"Financial Asset",G$6:G$15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="B38" s="19">
+        <f>SUMIF($B$6:$B$16,"Financial Asset",C$6:C$16)</f>
+        <v/>
+      </c>
+      <c r="C38" s="19">
+        <f>SUMIF($B$6:$B$16,"Financial Asset",D$6:D$16)</f>
+        <v/>
+      </c>
+      <c r="D38" s="19">
+        <f>SUMIF($B$6:$B$16,"Financial Asset",E$6:E$16)</f>
+        <v/>
+      </c>
+      <c r="E38" s="19">
+        <f>SUMIF($B$6:$B$16,"Financial Asset",F$6:F$16)</f>
+        <v/>
+      </c>
+      <c r="F38" s="19">
+        <f>SUMIF($B$6:$B$16,"Financial Asset",G$6:G$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Financial Liabilities</t>
         </is>
       </c>
-      <c r="B38" s="18">
-        <f>SUMIF($B$6:$B$15,"Financial Liability",C$6:C$15)</f>
-        <v/>
-      </c>
-      <c r="C38" s="18">
-        <f>SUMIF($B$6:$B$15,"Financial Liability",D$6:D$15)</f>
-        <v/>
-      </c>
-      <c r="D38" s="18">
-        <f>SUMIF($B$6:$B$15,"Financial Liability",E$6:E$15)</f>
-        <v/>
-      </c>
-      <c r="E38" s="18">
-        <f>SUMIF($B$6:$B$15,"Financial Liability",F$6:F$15)</f>
-        <v/>
-      </c>
-      <c r="F38" s="18">
-        <f>SUMIF($B$6:$B$15,"Financial Liability",G$6:G$15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="B39" s="19">
+        <f>SUMIF($B$6:$B$16,"Financial Liability",C$6:C$16)</f>
+        <v/>
+      </c>
+      <c r="C39" s="19">
+        <f>SUMIF($B$6:$B$16,"Financial Liability",D$6:D$16)</f>
+        <v/>
+      </c>
+      <c r="D39" s="19">
+        <f>SUMIF($B$6:$B$16,"Financial Liability",E$6:E$16)</f>
+        <v/>
+      </c>
+      <c r="E39" s="19">
+        <f>SUMIF($B$6:$B$16,"Financial Liability",F$6:F$16)</f>
+        <v/>
+      </c>
+      <c r="F39" s="19">
+        <f>SUMIF($B$6:$B$16,"Financial Liability",G$6:G$16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="B39" s="18">
-        <f>B38-B37</f>
-        <v/>
-      </c>
-      <c r="C39" s="18">
-        <f>C38-C37</f>
-        <v/>
-      </c>
-      <c r="D39" s="18">
-        <f>D38-D37</f>
-        <v/>
-      </c>
-      <c r="E39" s="18">
-        <f>E38-E37</f>
-        <v/>
-      </c>
-      <c r="F39" s="18">
-        <f>F38-F37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="B40" s="19">
+        <f>B39-B38</f>
+        <v/>
+      </c>
+      <c r="C40" s="19">
+        <f>C39-C38</f>
+        <v/>
+      </c>
+      <c r="D40" s="19">
+        <f>D39-D38</f>
+        <v/>
+      </c>
+      <c r="E40" s="19">
+        <f>E39-E38</f>
+        <v/>
+      </c>
+      <c r="F40" s="19">
+        <f>F39-F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Equity (NOA - Net Debt)</t>
         </is>
       </c>
-      <c r="B40" s="18">
-        <f>B36-B39</f>
-        <v/>
-      </c>
-      <c r="C40" s="18">
-        <f>C36-C39</f>
-        <v/>
-      </c>
-      <c r="D40" s="18">
-        <f>D36-D39</f>
-        <v/>
-      </c>
-      <c r="E40" s="18">
-        <f>E36-E39</f>
-        <v/>
-      </c>
-      <c r="F40" s="18">
-        <f>F36-F39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="B41" s="19">
+        <f>B37-B40</f>
+        <v/>
+      </c>
+      <c r="C41" s="19">
+        <f>C37-C40</f>
+        <v/>
+      </c>
+      <c r="D41" s="19">
+        <f>D37-D40</f>
+        <v/>
+      </c>
+      <c r="E41" s="19">
+        <f>E37-E40</f>
+        <v/>
+      </c>
+      <c r="F41" s="19">
+        <f>F37-F40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Reported Equity</t>
         </is>
       </c>
-      <c r="B41" s="14">
-        <f>'Balance Sheet'!B19</f>
-        <v/>
-      </c>
-      <c r="C41" s="14">
-        <f>'Balance Sheet'!C19</f>
-        <v/>
-      </c>
-      <c r="D41" s="14">
-        <f>'Balance Sheet'!D19</f>
-        <v/>
-      </c>
-      <c r="E41" s="14">
-        <f>'Balance Sheet'!E19</f>
-        <v/>
-      </c>
-      <c r="F41" s="14">
-        <f>'Balance Sheet'!F19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="B42" s="15">
+        <f>'Balance Sheet'!B20</f>
+        <v/>
+      </c>
+      <c r="C42" s="15">
+        <f>'Balance Sheet'!C20</f>
+        <v/>
+      </c>
+      <c r="D42" s="15">
+        <f>'Balance Sheet'!D20</f>
+        <v/>
+      </c>
+      <c r="E42" s="15">
+        <f>'Balance Sheet'!E20</f>
+        <v/>
+      </c>
+      <c r="F42" s="15">
+        <f>'Balance Sheet'!F20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Total Capital</t>
         </is>
       </c>
-      <c r="B42" s="14">
-        <f>B39+B40</f>
-        <v/>
-      </c>
-      <c r="C42" s="14">
-        <f>C39+C40</f>
-        <v/>
-      </c>
-      <c r="D42" s="14">
-        <f>D39+D40</f>
-        <v/>
-      </c>
-      <c r="E42" s="14">
-        <f>E39+E40</f>
-        <v/>
-      </c>
-      <c r="F42" s="14">
-        <f>F39+F40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="B43" s="15">
+        <f>B40+B41</f>
+        <v/>
+      </c>
+      <c r="C43" s="15">
+        <f>C40+C41</f>
+        <v/>
+      </c>
+      <c r="D43" s="15">
+        <f>D40+D41</f>
+        <v/>
+      </c>
+      <c r="E43" s="15">
+        <f>E40+E41</f>
+        <v/>
+      </c>
+      <c r="F43" s="15">
+        <f>F40+F41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
       </c>
-      <c r="B43" s="8">
-        <f>IF(ABS(B40-B41)&lt;1,"OK","CHECK")</f>
-        <v/>
-      </c>
-      <c r="C43" s="8">
-        <f>IF(ABS(C40-C41)&lt;1,"OK","CHECK")</f>
-        <v/>
-      </c>
-      <c r="D43" s="8">
-        <f>IF(ABS(D40-D41)&lt;1,"OK","CHECK")</f>
-        <v/>
-      </c>
-      <c r="E43" s="8">
-        <f>IF(ABS(E40-E41)&lt;1,"OK","CHECK")</f>
-        <v/>
-      </c>
-      <c r="F43" s="8">
-        <f>IF(ABS(F40-F41)&lt;1,"OK","CHECK")</f>
+      <c r="B44" s="9">
+        <f>IF(ABS(B41-B42)&lt;1,"OK","CHECK")</f>
+        <v/>
+      </c>
+      <c r="C44" s="9">
+        <f>IF(ABS(C41-C42)&lt;1,"OK","CHECK")</f>
+        <v/>
+      </c>
+      <c r="D44" s="9">
+        <f>IF(ABS(D41-D42)&lt;1,"OK","CHECK")</f>
+        <v/>
+      </c>
+      <c r="E44" s="9">
+        <f>IF(ABS(E41-E42)&lt;1,"OK","CHECK")</f>
+        <v/>
+      </c>
+      <c r="F44" s="9">
+        <f>IF(ABS(F41-F42)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Operating Working Capital Asset,Operating Working Capital Liability,Operating Long-Term Asset,Operating Long-Term Liability,Financial Asset,Financial Liability,Equity,Exclude"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13262,14 +13339,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Demo Holdings Limited — DuPont Decomposition</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>ROE = RNOA + FLEV × Spread</t>
         </is>
@@ -13277,247 +13354,247 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="13" t="n">
         <v>44561</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="13" t="n">
         <v>44926</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="13" t="n">
         <v>45291</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <v>45657</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="13" t="n">
         <v>46022</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Sales Growth</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C5" s="17">
-        <f>IF('Condensed Financials'!B18=0,0,'Condensed Financials'!C18/'Condensed Financials'!B18-1)</f>
-        <v/>
-      </c>
-      <c r="D5" s="17">
-        <f>IF('Condensed Financials'!C18=0,0,'Condensed Financials'!D18/'Condensed Financials'!C18-1)</f>
-        <v/>
-      </c>
-      <c r="E5" s="17">
-        <f>IF('Condensed Financials'!D18=0,0,'Condensed Financials'!E18/'Condensed Financials'!D18-1)</f>
-        <v/>
-      </c>
-      <c r="F5" s="17">
-        <f>IF('Condensed Financials'!E18=0,0,'Condensed Financials'!F18/'Condensed Financials'!E18-1)</f>
+      <c r="C5" s="18">
+        <f>IF('Condensed Financials'!B19=0,0,'Condensed Financials'!C19/'Condensed Financials'!B19-1)</f>
+        <v/>
+      </c>
+      <c r="D5" s="18">
+        <f>IF('Condensed Financials'!C19=0,0,'Condensed Financials'!D19/'Condensed Financials'!C19-1)</f>
+        <v/>
+      </c>
+      <c r="E5" s="18">
+        <f>IF('Condensed Financials'!D19=0,0,'Condensed Financials'!E19/'Condensed Financials'!D19-1)</f>
+        <v/>
+      </c>
+      <c r="F5" s="18">
+        <f>IF('Condensed Financials'!E19=0,0,'Condensed Financials'!F19/'Condensed Financials'!E19-1)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>NOPAT Margin</t>
         </is>
       </c>
-      <c r="B6" s="17">
-        <f>IF('Condensed Financials'!B18=0,0,'Condensed Financials'!B27/'Condensed Financials'!B18)</f>
-        <v/>
-      </c>
-      <c r="C6" s="17">
-        <f>IF('Condensed Financials'!C18=0,0,'Condensed Financials'!C27/'Condensed Financials'!C18)</f>
-        <v/>
-      </c>
-      <c r="D6" s="17">
-        <f>IF('Condensed Financials'!D18=0,0,'Condensed Financials'!D27/'Condensed Financials'!D18)</f>
-        <v/>
-      </c>
-      <c r="E6" s="17">
-        <f>IF('Condensed Financials'!E18=0,0,'Condensed Financials'!E27/'Condensed Financials'!E18)</f>
-        <v/>
-      </c>
-      <c r="F6" s="17">
-        <f>IF('Condensed Financials'!F18=0,0,'Condensed Financials'!F27/'Condensed Financials'!F18)</f>
+      <c r="B6" s="18">
+        <f>IF('Condensed Financials'!B19=0,0,'Condensed Financials'!B28/'Condensed Financials'!B19)</f>
+        <v/>
+      </c>
+      <c r="C6" s="18">
+        <f>IF('Condensed Financials'!C19=0,0,'Condensed Financials'!C28/'Condensed Financials'!C19)</f>
+        <v/>
+      </c>
+      <c r="D6" s="18">
+        <f>IF('Condensed Financials'!D19=0,0,'Condensed Financials'!D28/'Condensed Financials'!D19)</f>
+        <v/>
+      </c>
+      <c r="E6" s="18">
+        <f>IF('Condensed Financials'!E19=0,0,'Condensed Financials'!E28/'Condensed Financials'!E19)</f>
+        <v/>
+      </c>
+      <c r="F6" s="18">
+        <f>IF('Condensed Financials'!F19=0,0,'Condensed Financials'!F28/'Condensed Financials'!F19)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>RNOA</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C7" s="21">
-        <f>IF((('Condensed Financials'!C36+'Condensed Financials'!B36)/2)=0,0,'Condensed Financials'!C27/(('Condensed Financials'!C36+'Condensed Financials'!B36)/2))</f>
-        <v/>
-      </c>
-      <c r="D7" s="21">
-        <f>IF((('Condensed Financials'!D36+'Condensed Financials'!C36)/2)=0,0,'Condensed Financials'!D27/(('Condensed Financials'!D36+'Condensed Financials'!C36)/2))</f>
-        <v/>
-      </c>
-      <c r="E7" s="21">
-        <f>IF((('Condensed Financials'!E36+'Condensed Financials'!D36)/2)=0,0,'Condensed Financials'!E27/(('Condensed Financials'!E36+'Condensed Financials'!D36)/2))</f>
-        <v/>
-      </c>
-      <c r="F7" s="21">
-        <f>IF((('Condensed Financials'!F36+'Condensed Financials'!E36)/2)=0,0,'Condensed Financials'!F27/(('Condensed Financials'!F36+'Condensed Financials'!E36)/2))</f>
+      <c r="C7" s="22">
+        <f>IF((('Condensed Financials'!C37+'Condensed Financials'!B37)/2)=0,0,'Condensed Financials'!C28/(('Condensed Financials'!C37+'Condensed Financials'!B37)/2))</f>
+        <v/>
+      </c>
+      <c r="D7" s="22">
+        <f>IF((('Condensed Financials'!D37+'Condensed Financials'!C37)/2)=0,0,'Condensed Financials'!D28/(('Condensed Financials'!D37+'Condensed Financials'!C37)/2))</f>
+        <v/>
+      </c>
+      <c r="E7" s="22">
+        <f>IF((('Condensed Financials'!E37+'Condensed Financials'!D37)/2)=0,0,'Condensed Financials'!E28/(('Condensed Financials'!E37+'Condensed Financials'!D37)/2))</f>
+        <v/>
+      </c>
+      <c r="F7" s="22">
+        <f>IF((('Condensed Financials'!F37+'Condensed Financials'!E37)/2)=0,0,'Condensed Financials'!F28/(('Condensed Financials'!F37+'Condensed Financials'!E37)/2))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>After-tax CoD</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C8" s="17">
-        <f>IF((('Condensed Financials'!C39+'Condensed Financials'!B39)/2)=0,0,'Condensed Financials'!C26/(('Condensed Financials'!C39+'Condensed Financials'!B39)/2))</f>
-        <v/>
-      </c>
-      <c r="D8" s="17">
-        <f>IF((('Condensed Financials'!D39+'Condensed Financials'!C39)/2)=0,0,'Condensed Financials'!D26/(('Condensed Financials'!D39+'Condensed Financials'!C39)/2))</f>
-        <v/>
-      </c>
-      <c r="E8" s="17">
-        <f>IF((('Condensed Financials'!E39+'Condensed Financials'!D39)/2)=0,0,'Condensed Financials'!E26/(('Condensed Financials'!E39+'Condensed Financials'!D39)/2))</f>
-        <v/>
-      </c>
-      <c r="F8" s="17">
-        <f>IF((('Condensed Financials'!F39+'Condensed Financials'!E39)/2)=0,0,'Condensed Financials'!F26/(('Condensed Financials'!F39+'Condensed Financials'!E39)/2))</f>
+      <c r="C8" s="18">
+        <f>IF((('Condensed Financials'!C40+'Condensed Financials'!B40)/2)=0,0,'Condensed Financials'!C27/(('Condensed Financials'!C40+'Condensed Financials'!B40)/2))</f>
+        <v/>
+      </c>
+      <c r="D8" s="18">
+        <f>IF((('Condensed Financials'!D40+'Condensed Financials'!C40)/2)=0,0,'Condensed Financials'!D27/(('Condensed Financials'!D40+'Condensed Financials'!C40)/2))</f>
+        <v/>
+      </c>
+      <c r="E8" s="18">
+        <f>IF((('Condensed Financials'!E40+'Condensed Financials'!D40)/2)=0,0,'Condensed Financials'!E27/(('Condensed Financials'!E40+'Condensed Financials'!D40)/2))</f>
+        <v/>
+      </c>
+      <c r="F8" s="18">
+        <f>IF((('Condensed Financials'!F40+'Condensed Financials'!E40)/2)=0,0,'Condensed Financials'!F27/(('Condensed Financials'!F40+'Condensed Financials'!E40)/2))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="22">
         <f>C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="22">
         <f>D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="22">
         <f>E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="22">
         <f>F7-F8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>FLEV</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C10" s="15">
-        <f>IF((('Condensed Financials'!C40+'Condensed Financials'!B40)/2)=0,0,(('Condensed Financials'!C39+'Condensed Financials'!B39)/2)/(('Condensed Financials'!C40+'Condensed Financials'!B40)/2))</f>
-        <v/>
-      </c>
-      <c r="D10" s="15">
-        <f>IF((('Condensed Financials'!D40+'Condensed Financials'!C40)/2)=0,0,(('Condensed Financials'!D39+'Condensed Financials'!C39)/2)/(('Condensed Financials'!D40+'Condensed Financials'!C40)/2))</f>
-        <v/>
-      </c>
-      <c r="E10" s="15">
-        <f>IF((('Condensed Financials'!E40+'Condensed Financials'!D40)/2)=0,0,(('Condensed Financials'!E39+'Condensed Financials'!D39)/2)/(('Condensed Financials'!E40+'Condensed Financials'!D40)/2))</f>
-        <v/>
-      </c>
-      <c r="F10" s="15">
-        <f>IF((('Condensed Financials'!F40+'Condensed Financials'!E40)/2)=0,0,(('Condensed Financials'!F39+'Condensed Financials'!E39)/2)/(('Condensed Financials'!F40+'Condensed Financials'!E40)/2))</f>
+      <c r="C10" s="16">
+        <f>IF((('Condensed Financials'!C41+'Condensed Financials'!B41)/2)=0,0,(('Condensed Financials'!C40+'Condensed Financials'!B40)/2)/(('Condensed Financials'!C41+'Condensed Financials'!B41)/2))</f>
+        <v/>
+      </c>
+      <c r="D10" s="16">
+        <f>IF((('Condensed Financials'!D41+'Condensed Financials'!C41)/2)=0,0,(('Condensed Financials'!D40+'Condensed Financials'!C40)/2)/(('Condensed Financials'!D41+'Condensed Financials'!C41)/2))</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>IF((('Condensed Financials'!E41+'Condensed Financials'!D41)/2)=0,0,(('Condensed Financials'!E40+'Condensed Financials'!D40)/2)/(('Condensed Financials'!E41+'Condensed Financials'!D41)/2))</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>IF((('Condensed Financials'!F41+'Condensed Financials'!E41)/2)=0,0,(('Condensed Financials'!F40+'Condensed Financials'!E40)/2)/(('Condensed Financials'!F41+'Condensed Financials'!E41)/2))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>ROE (decomposed)</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="18">
         <f>C7+C10*(C9)</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <f>D7+D10*(D9)</f>
         <v/>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="18">
         <f>E7+E10*(E9)</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="18">
         <f>F7+F10*(F9)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Actual ROE</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C12" s="17">
-        <f>IF((('Condensed Financials'!C40+'Condensed Financials'!B40)/2)=0,0,'Condensed Financials'!C19/(('Condensed Financials'!C40+'Condensed Financials'!B40)/2))</f>
-        <v/>
-      </c>
-      <c r="D12" s="17">
-        <f>IF((('Condensed Financials'!D40+'Condensed Financials'!C40)/2)=0,0,'Condensed Financials'!D19/(('Condensed Financials'!D40+'Condensed Financials'!C40)/2))</f>
-        <v/>
-      </c>
-      <c r="E12" s="17">
-        <f>IF((('Condensed Financials'!E40+'Condensed Financials'!D40)/2)=0,0,'Condensed Financials'!E19/(('Condensed Financials'!E40+'Condensed Financials'!D40)/2))</f>
-        <v/>
-      </c>
-      <c r="F12" s="17">
-        <f>IF((('Condensed Financials'!F40+'Condensed Financials'!E40)/2)=0,0,'Condensed Financials'!F19/(('Condensed Financials'!F40+'Condensed Financials'!E40)/2))</f>
+      <c r="C12" s="18">
+        <f>IF((('Condensed Financials'!C41+'Condensed Financials'!B41)/2)=0,0,'Condensed Financials'!C20/(('Condensed Financials'!C41+'Condensed Financials'!B41)/2))</f>
+        <v/>
+      </c>
+      <c r="D12" s="18">
+        <f>IF((('Condensed Financials'!D41+'Condensed Financials'!C41)/2)=0,0,'Condensed Financials'!D20/(('Condensed Financials'!D41+'Condensed Financials'!C41)/2))</f>
+        <v/>
+      </c>
+      <c r="E12" s="18">
+        <f>IF((('Condensed Financials'!E41+'Condensed Financials'!D41)/2)=0,0,'Condensed Financials'!E20/(('Condensed Financials'!E41+'Condensed Financials'!D41)/2))</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f>IF((('Condensed Financials'!F41+'Condensed Financials'!E41)/2)=0,0,'Condensed Financials'!F20/(('Condensed Financials'!F41+'Condensed Financials'!E41)/2))</f>
         <v/>
       </c>
     </row>
@@ -13533,17 +13610,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Deferred from historical-only v1</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Accounting Judgment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>The supplied treatment is the model's reference treatment, not a universal accounting truth. Compare it with the listed alternative(s), choose the treatment you would defend, and explain the economic consequence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Supplied model treatment</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Alternative(s) to evaluate</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Your treatment</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Your rationale</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Your consequence explanation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Operating lease liabilities</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Lease liability operating vs financing</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Operating Long-Term Liability</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Financial Liability</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Operating Long-Term Liability</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>Lease liability concept — operating vs financial judgment</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>Operating treatment lowers NOLA/NOA; financing treatment raises Net Debt. The choice can shift RNOA versus FLEV/Spread interpretation while equity reconciliation should remain intact.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Operating Long-Term Liability,Financial Liability"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13558,7 +13740,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Deferred from historical-only v1</t>
         </is>
@@ -13579,7 +13761,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Deferred from historical-only v1</t>
         </is>
